--- a/outputs/cmo_gt_caitlin_v2.xlsx
+++ b/outputs/cmo_gt_caitlin_v2.xlsx
@@ -485,9 +485,6 @@
       <c r="D2" t="b">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,9 +505,6 @@
       <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,9 +525,6 @@
       <c r="D4" t="b">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -554,9 +545,6 @@
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,9 +565,6 @@
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -600,9 +585,6 @@
       <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -623,9 +605,6 @@
       <c r="D8" t="b">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -646,9 +625,6 @@
       <c r="D9" t="b">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -669,9 +645,6 @@
       <c r="D10" t="b">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -692,9 +665,6 @@
       <c r="D11" t="b">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -715,9 +685,6 @@
       <c r="D12" t="b">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -738,9 +705,6 @@
       <c r="D13" t="b">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -761,9 +725,6 @@
       <c r="D14" t="b">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -784,9 +745,6 @@
       <c r="D15" t="b">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -807,9 +765,6 @@
       <c r="D16" t="b">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -830,9 +785,6 @@
       <c r="D17" t="b">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -853,9 +805,6 @@
       <c r="D18" t="b">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -876,9 +825,6 @@
       <c r="D19" t="b">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -899,9 +845,6 @@
       <c r="D20" t="b">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -922,9 +865,6 @@
       <c r="D21" t="b">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -945,9 +885,6 @@
       <c r="D22" t="b">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -968,9 +905,6 @@
       <c r="D23" t="b">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -991,9 +925,6 @@
       <c r="D24" t="b">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1014,9 +945,6 @@
       <c r="D25" t="b">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1037,9 +965,6 @@
       <c r="D26" t="b">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1060,9 +985,6 @@
       <c r="D27" t="b">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1083,9 +1005,6 @@
       <c r="D28" t="b">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1106,9 +1025,6 @@
       <c r="D29" t="b">
         <v>1</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1129,9 +1045,6 @@
       <c r="D30" t="b">
         <v>1</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1152,9 +1065,6 @@
       <c r="D31" t="b">
         <v>1</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1175,9 +1085,6 @@
       <c r="D32" t="b">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1198,9 +1105,6 @@
       <c r="D33" t="b">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1221,9 +1125,6 @@
       <c r="D34" t="b">
         <v>1</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1244,9 +1145,6 @@
       <c r="D35" t="b">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1267,9 +1165,6 @@
       <c r="D36" t="b">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1290,9 +1185,6 @@
       <c r="D37" t="b">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1313,9 +1205,6 @@
       <c r="D38" t="b">
         <v>0</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1336,9 +1225,6 @@
       <c r="D39" t="b">
         <v>0</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1359,9 +1245,6 @@
       <c r="D40" t="b">
         <v>0</v>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1382,9 +1265,6 @@
       <c r="D41" t="b">
         <v>0</v>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1405,9 +1285,6 @@
       <c r="D42" t="b">
         <v>0</v>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1428,9 +1305,6 @@
       <c r="D43" t="b">
         <v>0</v>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1451,9 +1325,6 @@
       <c r="D44" t="b">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1474,9 +1345,6 @@
       <c r="D45" t="b">
         <v>0</v>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1497,9 +1365,6 @@
       <c r="D46" t="b">
         <v>0</v>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1520,9 +1385,6 @@
       <c r="D47" t="b">
         <v>0</v>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1543,9 +1405,6 @@
       <c r="D48" t="b">
         <v>0</v>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1566,9 +1425,6 @@
       <c r="D49" t="b">
         <v>0</v>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1589,9 +1445,6 @@
       <c r="D50" t="b">
         <v>0</v>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1612,9 +1465,6 @@
       <c r="D51" t="b">
         <v>1</v>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1635,9 +1485,6 @@
       <c r="D52" t="b">
         <v>1</v>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1658,9 +1505,6 @@
       <c r="D53" t="b">
         <v>1</v>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1681,9 +1525,6 @@
       <c r="D54" t="b">
         <v>1</v>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1704,9 +1545,6 @@
       <c r="D55" t="b">
         <v>1</v>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1727,9 +1565,6 @@
       <c r="D56" t="b">
         <v>1</v>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1750,9 +1585,6 @@
       <c r="D57" t="b">
         <v>1</v>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1773,9 +1605,6 @@
       <c r="D58" t="b">
         <v>1</v>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1796,9 +1625,6 @@
       <c r="D59" t="b">
         <v>1</v>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1819,9 +1645,6 @@
       <c r="D60" t="b">
         <v>0</v>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1842,9 +1665,6 @@
       <c r="D61" t="b">
         <v>0</v>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1865,9 +1685,6 @@
       <c r="D62" t="b">
         <v>0</v>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1888,9 +1705,6 @@
       <c r="D63" t="b">
         <v>0</v>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1911,9 +1725,6 @@
       <c r="D64" t="b">
         <v>0</v>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1934,9 +1745,6 @@
       <c r="D65" t="b">
         <v>0</v>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1957,9 +1765,6 @@
       <c r="D66" t="b">
         <v>0</v>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1980,9 +1785,6 @@
       <c r="D67" t="b">
         <v>0</v>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2003,9 +1805,6 @@
       <c r="D68" t="b">
         <v>0</v>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2026,9 +1825,6 @@
       <c r="D69" t="b">
         <v>0</v>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2049,9 +1845,6 @@
       <c r="D70" t="b">
         <v>0</v>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2072,9 +1865,6 @@
       <c r="D71" t="b">
         <v>0</v>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2095,9 +1885,6 @@
       <c r="D72" t="b">
         <v>0</v>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2118,9 +1905,6 @@
       <c r="D73" t="b">
         <v>0</v>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2141,9 +1925,6 @@
       <c r="D74" t="b">
         <v>0</v>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2164,9 +1945,6 @@
       <c r="D75" t="b">
         <v>1</v>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2187,9 +1965,6 @@
       <c r="D76" t="b">
         <v>1</v>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2210,9 +1985,6 @@
       <c r="D77" t="b">
         <v>1</v>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2233,9 +2005,6 @@
       <c r="D78" t="b">
         <v>1</v>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2256,9 +2025,6 @@
       <c r="D79" t="b">
         <v>0</v>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2279,9 +2045,6 @@
       <c r="D80" t="b">
         <v>0</v>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2302,9 +2065,6 @@
       <c r="D81" t="b">
         <v>0</v>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2325,9 +2085,6 @@
       <c r="D82" t="b">
         <v>0</v>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2348,9 +2105,6 @@
       <c r="D83" t="b">
         <v>0</v>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2371,9 +2125,6 @@
       <c r="D84" t="b">
         <v>0</v>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2394,9 +2145,6 @@
       <c r="D85" t="b">
         <v>0</v>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2417,9 +2165,6 @@
       <c r="D86" t="b">
         <v>0</v>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2440,9 +2185,6 @@
       <c r="D87" t="b">
         <v>0</v>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2463,9 +2205,6 @@
       <c r="D88" t="b">
         <v>0</v>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2486,9 +2225,6 @@
       <c r="D89" t="b">
         <v>0</v>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2509,9 +2245,6 @@
       <c r="D90" t="b">
         <v>0</v>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2532,9 +2265,6 @@
       <c r="D91" t="b">
         <v>0</v>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2555,9 +2285,6 @@
       <c r="D92" t="b">
         <v>0</v>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2578,9 +2305,6 @@
       <c r="D93" t="b">
         <v>0</v>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2601,9 +2325,6 @@
       <c r="D94" t="b">
         <v>1</v>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2624,9 +2345,6 @@
       <c r="D95" t="b">
         <v>1</v>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2647,9 +2365,6 @@
       <c r="D96" t="b">
         <v>0</v>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2670,9 +2385,6 @@
       <c r="D97" t="b">
         <v>0</v>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2693,9 +2405,6 @@
       <c r="D98" t="b">
         <v>0</v>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2716,9 +2425,6 @@
       <c r="D99" t="b">
         <v>0</v>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2739,9 +2445,6 @@
       <c r="D100" t="b">
         <v>0</v>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2762,9 +2465,6 @@
       <c r="D101" t="b">
         <v>0</v>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2785,9 +2485,6 @@
       <c r="D102" t="b">
         <v>0</v>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2808,9 +2505,6 @@
       <c r="D103" t="b">
         <v>0</v>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2831,9 +2525,6 @@
       <c r="D104" t="b">
         <v>0</v>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2854,9 +2545,6 @@
       <c r="D105" t="b">
         <v>0</v>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2877,9 +2565,6 @@
       <c r="D106" t="b">
         <v>0</v>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2900,9 +2585,6 @@
       <c r="D107" t="b">
         <v>0</v>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2923,9 +2605,6 @@
       <c r="D108" t="b">
         <v>0</v>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2946,9 +2625,6 @@
       <c r="D109" t="b">
         <v>0</v>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2969,9 +2645,6 @@
       <c r="D110" t="b">
         <v>0</v>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2992,9 +2665,6 @@
       <c r="D111" t="b">
         <v>1</v>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3015,9 +2685,6 @@
       <c r="D112" t="b">
         <v>1</v>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3038,9 +2705,6 @@
       <c r="D113" t="b">
         <v>1</v>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3061,9 +2725,6 @@
       <c r="D114" t="b">
         <v>1</v>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3084,9 +2745,6 @@
       <c r="D115" t="b">
         <v>1</v>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3107,9 +2765,6 @@
       <c r="D116" t="b">
         <v>1</v>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3130,9 +2785,6 @@
       <c r="D117" t="b">
         <v>1</v>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3153,9 +2805,6 @@
       <c r="D118" t="b">
         <v>1</v>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3176,9 +2825,6 @@
       <c r="D119" t="b">
         <v>1</v>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3199,9 +2845,6 @@
       <c r="D120" t="b">
         <v>0</v>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3222,9 +2865,6 @@
       <c r="D121" t="b">
         <v>0</v>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3245,9 +2885,6 @@
       <c r="D122" t="b">
         <v>0</v>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3268,9 +2905,6 @@
       <c r="D123" t="b">
         <v>0</v>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3291,9 +2925,6 @@
       <c r="D124" t="b">
         <v>0</v>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3314,9 +2945,6 @@
       <c r="D125" t="b">
         <v>0</v>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3337,9 +2965,6 @@
       <c r="D126" t="b">
         <v>1</v>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3360,9 +2985,6 @@
       <c r="D127" t="b">
         <v>0</v>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3383,9 +3005,6 @@
       <c r="D128" t="b">
         <v>0</v>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3406,9 +3025,6 @@
       <c r="D129" t="b">
         <v>0</v>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3429,9 +3045,6 @@
       <c r="D130" t="b">
         <v>0</v>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3452,9 +3065,6 @@
       <c r="D131" t="b">
         <v>0</v>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3475,9 +3085,6 @@
       <c r="D132" t="b">
         <v>0</v>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3498,9 +3105,6 @@
       <c r="D133" t="b">
         <v>0</v>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3521,9 +3125,6 @@
       <c r="D134" t="b">
         <v>1</v>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3544,9 +3145,6 @@
       <c r="D135" t="b">
         <v>1</v>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3567,9 +3165,6 @@
       <c r="D136" t="b">
         <v>0</v>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3590,9 +3185,6 @@
       <c r="D137" t="b">
         <v>0</v>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3613,9 +3205,6 @@
       <c r="D138" t="b">
         <v>0</v>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3636,9 +3225,6 @@
       <c r="D139" t="b">
         <v>0</v>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3659,9 +3245,6 @@
       <c r="D140" t="b">
         <v>0</v>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3682,9 +3265,6 @@
       <c r="D141" t="b">
         <v>0</v>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3705,9 +3285,6 @@
       <c r="D142" t="b">
         <v>0</v>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3728,9 +3305,6 @@
       <c r="D143" t="b">
         <v>0</v>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3751,9 +3325,6 @@
       <c r="D144" t="b">
         <v>0</v>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3774,9 +3345,6 @@
       <c r="D145" t="b">
         <v>0</v>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3797,9 +3365,6 @@
       <c r="D146" t="b">
         <v>0</v>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3820,9 +3385,6 @@
       <c r="D147" t="b">
         <v>0</v>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3843,9 +3405,6 @@
       <c r="D148" t="b">
         <v>0</v>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3866,9 +3425,6 @@
       <c r="D149" t="b">
         <v>0</v>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3889,9 +3445,6 @@
       <c r="D150" t="b">
         <v>0</v>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3912,9 +3465,6 @@
       <c r="D151" t="b">
         <v>1</v>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3935,9 +3485,6 @@
       <c r="D152" t="b">
         <v>1</v>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3958,9 +3505,6 @@
       <c r="D153" t="b">
         <v>0</v>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3981,9 +3525,6 @@
       <c r="D154" t="b">
         <v>0</v>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4004,9 +3545,6 @@
       <c r="D155" t="b">
         <v>0</v>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4027,9 +3565,6 @@
       <c r="D156" t="b">
         <v>0</v>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4050,9 +3585,6 @@
       <c r="D157" t="b">
         <v>0</v>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4073,9 +3605,6 @@
       <c r="D158" t="b">
         <v>0</v>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4096,9 +3625,6 @@
       <c r="D159" t="b">
         <v>0</v>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4119,9 +3645,6 @@
       <c r="D160" t="b">
         <v>0</v>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4142,9 +3665,6 @@
       <c r="D161" t="b">
         <v>0</v>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4165,9 +3685,6 @@
       <c r="D162" t="b">
         <v>0</v>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4188,9 +3705,6 @@
       <c r="D163" t="b">
         <v>0</v>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4211,9 +3725,6 @@
       <c r="D164" t="b">
         <v>0</v>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4234,9 +3745,6 @@
       <c r="D165" t="b">
         <v>0</v>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4257,9 +3765,6 @@
       <c r="D166" t="b">
         <v>0</v>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4280,9 +3785,6 @@
       <c r="D167" t="b">
         <v>0</v>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4303,9 +3805,6 @@
       <c r="D168" t="b">
         <v>1</v>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4326,9 +3825,6 @@
       <c r="D169" t="b">
         <v>0</v>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4349,9 +3845,6 @@
       <c r="D170" t="b">
         <v>0</v>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4372,9 +3865,6 @@
       <c r="D171" t="b">
         <v>0</v>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4395,9 +3885,6 @@
       <c r="D172" t="b">
         <v>0</v>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4418,9 +3905,6 @@
       <c r="D173" t="b">
         <v>0</v>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4441,9 +3925,6 @@
       <c r="D174" t="b">
         <v>0</v>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4464,9 +3945,6 @@
       <c r="D175" t="b">
         <v>0</v>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4487,9 +3965,6 @@
       <c r="D176" t="b">
         <v>0</v>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4510,9 +3985,6 @@
       <c r="D177" t="b">
         <v>0</v>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4533,9 +4005,6 @@
       <c r="D178" t="b">
         <v>0</v>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4556,9 +4025,6 @@
       <c r="D179" t="b">
         <v>0</v>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4579,9 +4045,6 @@
       <c r="D180" t="b">
         <v>0</v>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4602,9 +4065,6 @@
       <c r="D181" t="b">
         <v>0</v>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4625,9 +4085,6 @@
       <c r="D182" t="b">
         <v>0</v>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4648,9 +4105,6 @@
       <c r="D183" t="b">
         <v>0</v>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4671,9 +4125,6 @@
       <c r="D184" t="b">
         <v>0</v>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4694,9 +4145,6 @@
       <c r="D185" t="b">
         <v>1</v>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4717,9 +4165,6 @@
       <c r="D186" t="b">
         <v>1</v>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4740,9 +4185,6 @@
       <c r="D187" t="b">
         <v>0</v>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4763,9 +4205,6 @@
       <c r="D188" t="b">
         <v>0</v>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4786,9 +4225,6 @@
       <c r="D189" t="b">
         <v>0</v>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4809,9 +4245,6 @@
       <c r="D190" t="b">
         <v>0</v>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4832,9 +4265,6 @@
       <c r="D191" t="b">
         <v>0</v>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4855,9 +4285,6 @@
       <c r="D192" t="b">
         <v>0</v>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4878,9 +4305,6 @@
       <c r="D193" t="b">
         <v>0</v>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4901,9 +4325,6 @@
       <c r="D194" t="b">
         <v>0</v>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4924,9 +4345,6 @@
       <c r="D195" t="b">
         <v>0</v>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4947,9 +4365,6 @@
       <c r="D196" t="b">
         <v>0</v>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4970,9 +4385,6 @@
       <c r="D197" t="b">
         <v>0</v>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4993,9 +4405,6 @@
       <c r="D198" t="b">
         <v>0</v>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5016,9 +4425,6 @@
       <c r="D199" t="b">
         <v>0</v>
       </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5039,9 +4445,6 @@
       <c r="D200" t="b">
         <v>0</v>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5062,9 +4465,6 @@
       <c r="D201" t="b">
         <v>0</v>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5085,9 +4485,6 @@
       <c r="D202" t="b">
         <v>1</v>
       </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5108,9 +4505,6 @@
       <c r="D203" t="b">
         <v>1</v>
       </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5131,9 +4525,6 @@
       <c r="D204" t="b">
         <v>1</v>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5154,9 +4545,6 @@
       <c r="D205" t="b">
         <v>1</v>
       </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5177,9 +4565,6 @@
       <c r="D206" t="b">
         <v>1</v>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5200,9 +4585,6 @@
       <c r="D207" t="b">
         <v>1</v>
       </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5223,9 +4605,6 @@
       <c r="D208" t="b">
         <v>0</v>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5246,9 +4625,6 @@
       <c r="D209" t="b">
         <v>0</v>
       </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5269,9 +4645,6 @@
       <c r="D210" t="b">
         <v>0</v>
       </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5292,9 +4665,6 @@
       <c r="D211" t="b">
         <v>0</v>
       </c>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5315,9 +4685,6 @@
       <c r="D212" t="b">
         <v>0</v>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5338,9 +4705,6 @@
       <c r="D213" t="b">
         <v>0</v>
       </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5361,9 +4725,6 @@
       <c r="D214" t="b">
         <v>0</v>
       </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5384,9 +4745,6 @@
       <c r="D215" t="b">
         <v>1</v>
       </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5407,9 +4765,6 @@
       <c r="D216" t="b">
         <v>0</v>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5430,9 +4785,6 @@
       <c r="D217" t="b">
         <v>0</v>
       </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5453,9 +4805,6 @@
       <c r="D218" t="b">
         <v>0</v>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5476,9 +4825,6 @@
       <c r="D219" t="b">
         <v>0</v>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5499,9 +4845,6 @@
       <c r="D220" t="b">
         <v>0</v>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5522,9 +4865,6 @@
       <c r="D221" t="b">
         <v>0</v>
       </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5545,9 +4885,6 @@
       <c r="D222" t="b">
         <v>0</v>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5568,9 +4905,6 @@
       <c r="D223" t="b">
         <v>1</v>
       </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5591,9 +4925,6 @@
       <c r="D224" t="b">
         <v>1</v>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5614,9 +4945,6 @@
       <c r="D225" t="b">
         <v>1</v>
       </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5637,9 +4965,6 @@
       <c r="D226" t="b">
         <v>1</v>
       </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5660,9 +4985,6 @@
       <c r="D227" t="b">
         <v>1</v>
       </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5683,9 +5005,6 @@
       <c r="D228" t="b">
         <v>1</v>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5706,9 +5025,6 @@
       <c r="D229" t="b">
         <v>1</v>
       </c>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5729,9 +5045,6 @@
       <c r="D230" t="b">
         <v>1</v>
       </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5752,9 +5065,6 @@
       <c r="D231" t="b">
         <v>1</v>
       </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5775,9 +5085,6 @@
       <c r="D232" t="b">
         <v>1</v>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5798,9 +5105,6 @@
       <c r="D233" t="b">
         <v>1</v>
       </c>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5821,9 +5125,6 @@
       <c r="D234" t="b">
         <v>1</v>
       </c>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5844,9 +5145,6 @@
       <c r="D235" t="b">
         <v>1</v>
       </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5867,9 +5165,6 @@
       <c r="D236" t="b">
         <v>0</v>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5890,9 +5185,6 @@
       <c r="D237" t="b">
         <v>0</v>
       </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5913,9 +5205,6 @@
       <c r="D238" t="b">
         <v>0</v>
       </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5936,9 +5225,6 @@
       <c r="D239" t="b">
         <v>0</v>
       </c>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5959,9 +5245,6 @@
       <c r="D240" t="b">
         <v>0</v>
       </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5982,9 +5265,6 @@
       <c r="D241" t="b">
         <v>0</v>
       </c>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6005,9 +5285,6 @@
       <c r="D242" t="b">
         <v>0</v>
       </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6028,9 +5305,6 @@
       <c r="D243" t="b">
         <v>1</v>
       </c>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6051,9 +5325,6 @@
       <c r="D244" t="b">
         <v>0</v>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6074,9 +5345,6 @@
       <c r="D245" t="b">
         <v>0</v>
       </c>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6097,9 +5365,6 @@
       <c r="D246" t="b">
         <v>0</v>
       </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6120,9 +5385,6 @@
       <c r="D247" t="b">
         <v>0</v>
       </c>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -6143,9 +5405,6 @@
       <c r="D248" t="b">
         <v>0</v>
       </c>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6166,9 +5425,6 @@
       <c r="D249" t="b">
         <v>0</v>
       </c>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -6189,9 +5445,6 @@
       <c r="D250" t="b">
         <v>1</v>
       </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6212,9 +5465,6 @@
       <c r="D251" t="b">
         <v>1</v>
       </c>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -6235,9 +5485,6 @@
       <c r="D252" t="b">
         <v>0</v>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6258,9 +5505,6 @@
       <c r="D253" t="b">
         <v>0</v>
       </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6281,9 +5525,6 @@
       <c r="D254" t="b">
         <v>0</v>
       </c>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6304,9 +5545,6 @@
       <c r="D255" t="b">
         <v>0</v>
       </c>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6327,9 +5565,6 @@
       <c r="D256" t="b">
         <v>0</v>
       </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6350,9 +5585,6 @@
       <c r="D257" t="b">
         <v>0</v>
       </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6373,9 +5605,6 @@
       <c r="D258" t="b">
         <v>0</v>
       </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6396,9 +5625,6 @@
       <c r="D259" t="b">
         <v>1</v>
       </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6419,9 +5645,6 @@
       <c r="D260" t="b">
         <v>0</v>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6442,9 +5665,6 @@
       <c r="D261" t="b">
         <v>0</v>
       </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6465,9 +5685,6 @@
       <c r="D262" t="b">
         <v>0</v>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6488,9 +5705,6 @@
       <c r="D263" t="b">
         <v>0</v>
       </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6511,9 +5725,6 @@
       <c r="D264" t="b">
         <v>0</v>
       </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6534,9 +5745,6 @@
       <c r="D265" t="b">
         <v>0</v>
       </c>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6557,9 +5765,6 @@
       <c r="D266" t="b">
         <v>0</v>
       </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6580,9 +5785,6 @@
       <c r="D267" t="b">
         <v>1</v>
       </c>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6603,9 +5805,6 @@
       <c r="D268" t="b">
         <v>1</v>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6626,9 +5825,6 @@
       <c r="D269" t="b">
         <v>0</v>
       </c>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6649,9 +5845,6 @@
       <c r="D270" t="b">
         <v>0</v>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6672,9 +5865,6 @@
       <c r="D271" t="b">
         <v>0</v>
       </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6695,9 +5885,6 @@
       <c r="D272" t="b">
         <v>0</v>
       </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6718,9 +5905,6 @@
       <c r="D273" t="b">
         <v>0</v>
       </c>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6741,9 +5925,6 @@
       <c r="D274" t="b">
         <v>0</v>
       </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6764,9 +5945,6 @@
       <c r="D275" t="b">
         <v>0</v>
       </c>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6787,9 +5965,6 @@
       <c r="D276" t="b">
         <v>0</v>
       </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6810,9 +5985,6 @@
       <c r="D277" t="b">
         <v>0</v>
       </c>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6833,9 +6005,6 @@
       <c r="D278" t="b">
         <v>0</v>
       </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6856,9 +6025,6 @@
       <c r="D279" t="b">
         <v>0</v>
       </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6879,9 +6045,6 @@
       <c r="D280" t="b">
         <v>0</v>
       </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6902,9 +6065,6 @@
       <c r="D281" t="b">
         <v>0</v>
       </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6925,9 +6085,6 @@
       <c r="D282" t="b">
         <v>0</v>
       </c>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6948,9 +6105,6 @@
       <c r="D283" t="b">
         <v>0</v>
       </c>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6971,9 +6125,6 @@
       <c r="D284" t="b">
         <v>1</v>
       </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6994,9 +6145,6 @@
       <c r="D285" t="b">
         <v>1</v>
       </c>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7017,9 +6165,6 @@
       <c r="D286" t="b">
         <v>0</v>
       </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7040,9 +6185,6 @@
       <c r="D287" t="b">
         <v>0</v>
       </c>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7063,9 +6205,6 @@
       <c r="D288" t="b">
         <v>0</v>
       </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7086,9 +6225,6 @@
       <c r="D289" t="b">
         <v>0</v>
       </c>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -7109,9 +6245,6 @@
       <c r="D290" t="b">
         <v>0</v>
       </c>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7132,9 +6265,6 @@
       <c r="D291" t="b">
         <v>0</v>
       </c>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -7155,9 +6285,6 @@
       <c r="D292" t="b">
         <v>0</v>
       </c>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7178,9 +6305,6 @@
       <c r="D293" t="b">
         <v>0</v>
       </c>
-      <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -7201,9 +6325,6 @@
       <c r="D294" t="b">
         <v>0</v>
       </c>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -7224,9 +6345,6 @@
       <c r="D295" t="b">
         <v>0</v>
       </c>
-      <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -7247,9 +6365,6 @@
       <c r="D296" t="b">
         <v>0</v>
       </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -7270,9 +6385,6 @@
       <c r="D297" t="b">
         <v>0</v>
       </c>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7293,9 +6405,6 @@
       <c r="D298" t="b">
         <v>0</v>
       </c>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7316,9 +6425,6 @@
       <c r="D299" t="b">
         <v>0</v>
       </c>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7339,9 +6445,6 @@
       <c r="D300" t="b">
         <v>0</v>
       </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7362,9 +6465,6 @@
       <c r="D301" t="b">
         <v>1</v>
       </c>
-      <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7385,9 +6485,6 @@
       <c r="D302" t="b">
         <v>1</v>
       </c>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7408,9 +6505,6 @@
       <c r="D303" t="b">
         <v>0</v>
       </c>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7431,9 +6525,6 @@
       <c r="D304" t="b">
         <v>0</v>
       </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7454,9 +6545,6 @@
       <c r="D305" t="b">
         <v>0</v>
       </c>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7477,9 +6565,6 @@
       <c r="D306" t="b">
         <v>0</v>
       </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7500,9 +6585,6 @@
       <c r="D307" t="b">
         <v>0</v>
       </c>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7523,9 +6605,6 @@
       <c r="D308" t="b">
         <v>0</v>
       </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7546,9 +6625,6 @@
       <c r="D309" t="b">
         <v>0</v>
       </c>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7569,9 +6645,6 @@
       <c r="D310" t="b">
         <v>0</v>
       </c>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7592,9 +6665,6 @@
       <c r="D311" t="b">
         <v>0</v>
       </c>
-      <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7615,9 +6685,6 @@
       <c r="D312" t="b">
         <v>0</v>
       </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7638,9 +6705,6 @@
       <c r="D313" t="b">
         <v>0</v>
       </c>
-      <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
-      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7661,9 +6725,6 @@
       <c r="D314" t="b">
         <v>0</v>
       </c>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7684,9 +6745,6 @@
       <c r="D315" t="b">
         <v>0</v>
       </c>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7707,9 +6765,6 @@
       <c r="D316" t="b">
         <v>0</v>
       </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7730,9 +6785,6 @@
       <c r="D317" t="b">
         <v>0</v>
       </c>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7753,9 +6805,6 @@
       <c r="D318" t="b">
         <v>1</v>
       </c>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7776,9 +6825,6 @@
       <c r="D319" t="b">
         <v>1</v>
       </c>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7799,9 +6845,6 @@
       <c r="D320" t="b">
         <v>1</v>
       </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7822,9 +6865,6 @@
       <c r="D321" t="b">
         <v>1</v>
       </c>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
-      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7845,9 +6885,6 @@
       <c r="D322" t="b">
         <v>1</v>
       </c>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7868,9 +6905,6 @@
       <c r="D323" t="b">
         <v>1</v>
       </c>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7891,9 +6925,6 @@
       <c r="D324" t="b">
         <v>1</v>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7914,9 +6945,6 @@
       <c r="D325" t="b">
         <v>0</v>
       </c>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
-      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7937,9 +6965,6 @@
       <c r="D326" t="b">
         <v>0</v>
       </c>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7960,9 +6985,6 @@
       <c r="D327" t="b">
         <v>0</v>
       </c>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7983,9 +7005,6 @@
       <c r="D328" t="b">
         <v>0</v>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -8006,9 +7025,6 @@
       <c r="D329" t="b">
         <v>0</v>
       </c>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -8029,9 +7045,6 @@
       <c r="D330" t="b">
         <v>0</v>
       </c>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -8052,9 +7065,6 @@
       <c r="D331" t="b">
         <v>0</v>
       </c>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -8075,9 +7085,6 @@
       <c r="D332" t="b">
         <v>0</v>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -8098,9 +7105,6 @@
       <c r="D333" t="b">
         <v>0</v>
       </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -8121,9 +7125,6 @@
       <c r="D334" t="b">
         <v>0</v>
       </c>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -8144,9 +7145,6 @@
       <c r="D335" t="b">
         <v>0</v>
       </c>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -8167,9 +7165,6 @@
       <c r="D336" t="b">
         <v>0</v>
       </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -8190,9 +7185,6 @@
       <c r="D337" t="b">
         <v>0</v>
       </c>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -8213,9 +7205,6 @@
       <c r="D338" t="b">
         <v>0</v>
       </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -8236,9 +7225,6 @@
       <c r="D339" t="b">
         <v>0</v>
       </c>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -8259,9 +7245,6 @@
       <c r="D340" t="b">
         <v>1</v>
       </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -8282,9 +7265,6 @@
       <c r="D341" t="b">
         <v>1</v>
       </c>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -8305,9 +7285,6 @@
       <c r="D342" t="b">
         <v>1</v>
       </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -8328,9 +7305,6 @@
       <c r="D343" t="b">
         <v>1</v>
       </c>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8351,9 +7325,6 @@
       <c r="D344" t="b">
         <v>1</v>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8374,9 +7345,6 @@
       <c r="D345" t="b">
         <v>1</v>
       </c>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8397,9 +7365,6 @@
       <c r="D346" t="b">
         <v>0</v>
       </c>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8420,9 +7385,6 @@
       <c r="D347" t="b">
         <v>0</v>
       </c>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
-      <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8443,9 +7405,6 @@
       <c r="D348" t="b">
         <v>0</v>
       </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8466,9 +7425,6 @@
       <c r="D349" t="b">
         <v>0</v>
       </c>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8489,9 +7445,6 @@
       <c r="D350" t="b">
         <v>0</v>
       </c>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8512,9 +7465,6 @@
       <c r="D351" t="b">
         <v>0</v>
       </c>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8535,9 +7485,6 @@
       <c r="D352" t="b">
         <v>0</v>
       </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8558,9 +7505,6 @@
       <c r="D353" t="b">
         <v>1</v>
       </c>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8581,9 +7525,6 @@
       <c r="D354" t="b">
         <v>0</v>
       </c>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8604,9 +7545,6 @@
       <c r="D355" t="b">
         <v>0</v>
       </c>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
-      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8627,9 +7565,6 @@
       <c r="D356" t="b">
         <v>0</v>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8650,9 +7585,6 @@
       <c r="D357" t="b">
         <v>0</v>
       </c>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8673,9 +7605,6 @@
       <c r="D358" t="b">
         <v>0</v>
       </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8696,9 +7625,6 @@
       <c r="D359" t="b">
         <v>0</v>
       </c>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8719,9 +7645,6 @@
       <c r="D360" t="b">
         <v>0</v>
       </c>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8742,9 +7665,6 @@
       <c r="D361" t="b">
         <v>1</v>
       </c>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8765,9 +7685,6 @@
       <c r="D362" t="b">
         <v>1</v>
       </c>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8788,9 +7705,6 @@
       <c r="D363" t="b">
         <v>1</v>
       </c>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8811,9 +7725,6 @@
       <c r="D364" t="b">
         <v>1</v>
       </c>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8834,9 +7745,6 @@
       <c r="D365" t="b">
         <v>1</v>
       </c>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8857,9 +7765,6 @@
       <c r="D366" t="b">
         <v>0</v>
       </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8880,9 +7785,6 @@
       <c r="D367" t="b">
         <v>0</v>
       </c>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8903,9 +7805,6 @@
       <c r="D368" t="b">
         <v>0</v>
       </c>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8926,9 +7825,6 @@
       <c r="D369" t="b">
         <v>0</v>
       </c>
-      <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8949,9 +7845,6 @@
       <c r="D370" t="b">
         <v>0</v>
       </c>
-      <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8972,9 +7865,6 @@
       <c r="D371" t="b">
         <v>0</v>
       </c>
-      <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8995,9 +7885,6 @@
       <c r="D372" t="b">
         <v>0</v>
       </c>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -9018,9 +7905,6 @@
       <c r="D373" t="b">
         <v>0</v>
       </c>
-      <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -9041,9 +7925,6 @@
       <c r="D374" t="b">
         <v>0</v>
       </c>
-      <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -9064,9 +7945,6 @@
       <c r="D375" t="b">
         <v>0</v>
       </c>
-      <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -9087,9 +7965,6 @@
       <c r="D376" t="b">
         <v>0</v>
       </c>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -9110,9 +7985,6 @@
       <c r="D377" t="b">
         <v>0</v>
       </c>
-      <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -9133,9 +8005,6 @@
       <c r="D378" t="b">
         <v>0</v>
       </c>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -9156,9 +8025,6 @@
       <c r="D379" t="b">
         <v>0</v>
       </c>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -9179,9 +8045,6 @@
       <c r="D380" t="b">
         <v>0</v>
       </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -9202,9 +8065,6 @@
       <c r="D381" t="b">
         <v>1</v>
       </c>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -9225,9 +8085,6 @@
       <c r="D382" t="b">
         <v>1</v>
       </c>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -9248,9 +8105,6 @@
       <c r="D383" t="b">
         <v>1</v>
       </c>
-      <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -9271,9 +8125,6 @@
       <c r="D384" t="b">
         <v>1</v>
       </c>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -9294,9 +8145,6 @@
       <c r="D385" t="b">
         <v>1</v>
       </c>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -9317,9 +8165,6 @@
       <c r="D386" t="b">
         <v>1</v>
       </c>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -9340,9 +8185,6 @@
       <c r="D387" t="b">
         <v>0</v>
       </c>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -9363,9 +8205,6 @@
       <c r="D388" t="b">
         <v>0</v>
       </c>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9386,9 +8225,6 @@
       <c r="D389" t="b">
         <v>0</v>
       </c>
-      <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9409,9 +8245,6 @@
       <c r="D390" t="b">
         <v>0</v>
       </c>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9432,9 +8265,6 @@
       <c r="D391" t="b">
         <v>0</v>
       </c>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9455,9 +8285,6 @@
       <c r="D392" t="b">
         <v>0</v>
       </c>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9478,9 +8305,6 @@
       <c r="D393" t="b">
         <v>0</v>
       </c>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9501,9 +8325,6 @@
       <c r="D394" t="b">
         <v>1</v>
       </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9524,9 +8345,6 @@
       <c r="D395" t="b">
         <v>0</v>
       </c>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9547,9 +8365,6 @@
       <c r="D396" t="b">
         <v>0</v>
       </c>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9570,9 +8385,6 @@
       <c r="D397" t="b">
         <v>0</v>
       </c>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9593,9 +8405,6 @@
       <c r="D398" t="b">
         <v>0</v>
       </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -9616,9 +8425,6 @@
       <c r="D399" t="b">
         <v>0</v>
       </c>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -9639,9 +8445,6 @@
       <c r="D400" t="b">
         <v>0</v>
       </c>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -9662,9 +8465,6 @@
       <c r="D401" t="b">
         <v>0</v>
       </c>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -9685,9 +8485,6 @@
       <c r="D402" t="b">
         <v>1</v>
       </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -9708,9 +8505,6 @@
       <c r="D403" t="b">
         <v>0</v>
       </c>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -9731,9 +8525,6 @@
       <c r="D404" t="b">
         <v>0</v>
       </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -9754,9 +8545,6 @@
       <c r="D405" t="b">
         <v>0</v>
       </c>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -9777,9 +8565,6 @@
       <c r="D406" t="b">
         <v>0</v>
       </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -9800,9 +8585,6 @@
       <c r="D407" t="b">
         <v>0</v>
       </c>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9823,9 +8605,6 @@
       <c r="D408" t="b">
         <v>0</v>
       </c>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9846,9 +8625,6 @@
       <c r="D409" t="b">
         <v>0</v>
       </c>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9869,9 +8645,6 @@
       <c r="D410" t="b">
         <v>0</v>
       </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9892,9 +8665,6 @@
       <c r="D411" t="b">
         <v>0</v>
       </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9915,9 +8685,6 @@
       <c r="D412" t="b">
         <v>0</v>
       </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9938,9 +8705,6 @@
       <c r="D413" t="b">
         <v>0</v>
       </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9961,9 +8725,6 @@
       <c r="D414" t="b">
         <v>0</v>
       </c>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9984,9 +8745,6 @@
       <c r="D415" t="b">
         <v>0</v>
       </c>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -10007,9 +8765,6 @@
       <c r="D416" t="b">
         <v>0</v>
       </c>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -10030,9 +8785,6 @@
       <c r="D417" t="b">
         <v>0</v>
       </c>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -10053,9 +8805,6 @@
       <c r="D418" t="b">
         <v>0</v>
       </c>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -10076,9 +8825,6 @@
       <c r="D419" t="b">
         <v>1</v>
       </c>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -10099,9 +8845,6 @@
       <c r="D420" t="b">
         <v>1</v>
       </c>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -10122,9 +8865,6 @@
       <c r="D421" t="b">
         <v>1</v>
       </c>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -10145,9 +8885,6 @@
       <c r="D422" t="b">
         <v>0</v>
       </c>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -10168,9 +8905,6 @@
       <c r="D423" t="b">
         <v>0</v>
       </c>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -10191,9 +8925,6 @@
       <c r="D424" t="b">
         <v>0</v>
       </c>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -10214,9 +8945,6 @@
       <c r="D425" t="b">
         <v>0</v>
       </c>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -10237,9 +8965,6 @@
       <c r="D426" t="b">
         <v>0</v>
       </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -10260,9 +8985,6 @@
       <c r="D427" t="b">
         <v>0</v>
       </c>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -10283,9 +9005,6 @@
       <c r="D428" t="b">
         <v>0</v>
       </c>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -10306,9 +9025,6 @@
       <c r="D429" t="b">
         <v>1</v>
       </c>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -10329,9 +9045,6 @@
       <c r="D430" t="b">
         <v>0</v>
       </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -10352,9 +9065,6 @@
       <c r="D431" t="b">
         <v>0</v>
       </c>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -10375,9 +9085,6 @@
       <c r="D432" t="b">
         <v>0</v>
       </c>
-      <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -10398,9 +9105,6 @@
       <c r="D433" t="b">
         <v>0</v>
       </c>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -10421,9 +9125,6 @@
       <c r="D434" t="b">
         <v>0</v>
       </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -10444,9 +9145,6 @@
       <c r="D435" t="b">
         <v>0</v>
       </c>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -10467,9 +9165,6 @@
       <c r="D436" t="b">
         <v>0</v>
       </c>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -10490,9 +9185,6 @@
       <c r="D437" t="b">
         <v>0</v>
       </c>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -10513,9 +9205,6 @@
       <c r="D438" t="b">
         <v>1</v>
       </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -10536,9 +9225,6 @@
       <c r="D439" t="b">
         <v>1</v>
       </c>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -10559,9 +9245,6 @@
       <c r="D440" t="b">
         <v>0</v>
       </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -10582,9 +9265,6 @@
       <c r="D441" t="b">
         <v>0</v>
       </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -10605,9 +9285,6 @@
       <c r="D442" t="b">
         <v>0</v>
       </c>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -10628,9 +9305,6 @@
       <c r="D443" t="b">
         <v>0</v>
       </c>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -10651,9 +9325,6 @@
       <c r="D444" t="b">
         <v>0</v>
       </c>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -10674,9 +9345,6 @@
       <c r="D445" t="b">
         <v>0</v>
       </c>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -10697,9 +9365,6 @@
       <c r="D446" t="b">
         <v>0</v>
       </c>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -10720,9 +9385,6 @@
       <c r="D447" t="b">
         <v>0</v>
       </c>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -10743,9 +9405,6 @@
       <c r="D448" t="b">
         <v>0</v>
       </c>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -10766,9 +9425,6 @@
       <c r="D449" t="b">
         <v>0</v>
       </c>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -10789,9 +9445,6 @@
       <c r="D450" t="b">
         <v>0</v>
       </c>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -10812,9 +9465,6 @@
       <c r="D451" t="b">
         <v>0</v>
       </c>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -10835,9 +9485,6 @@
       <c r="D452" t="b">
         <v>0</v>
       </c>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -10858,9 +9505,6 @@
       <c r="D453" t="b">
         <v>0</v>
       </c>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -10881,9 +9525,6 @@
       <c r="D454" t="b">
         <v>0</v>
       </c>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -10904,9 +9545,6 @@
       <c r="D455" t="b">
         <v>1</v>
       </c>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10927,9 +9565,6 @@
       <c r="D456" t="b">
         <v>1</v>
       </c>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10950,9 +9585,6 @@
       <c r="D457" t="b">
         <v>1</v>
       </c>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10973,9 +9605,6 @@
       <c r="D458" t="b">
         <v>0</v>
       </c>
-      <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
-      <c r="G458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10996,9 +9625,6 @@
       <c r="D459" t="b">
         <v>0</v>
       </c>
-      <c r="E459" t="inlineStr"/>
-      <c r="F459" t="inlineStr"/>
-      <c r="G459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -11019,9 +9645,6 @@
       <c r="D460" t="b">
         <v>0</v>
       </c>
-      <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
-      <c r="G460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -11042,9 +9665,6 @@
       <c r="D461" t="b">
         <v>0</v>
       </c>
-      <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
-      <c r="G461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -11065,9 +9685,6 @@
       <c r="D462" t="b">
         <v>0</v>
       </c>
-      <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
-      <c r="G462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -11088,9 +9705,6 @@
       <c r="D463" t="b">
         <v>0</v>
       </c>
-      <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
-      <c r="G463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -11111,9 +9725,6 @@
       <c r="D464" t="b">
         <v>0</v>
       </c>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
-      <c r="G464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -11134,9 +9745,6 @@
       <c r="D465" t="b">
         <v>0</v>
       </c>
-      <c r="E465" t="inlineStr"/>
-      <c r="F465" t="inlineStr"/>
-      <c r="G465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -11157,9 +9765,6 @@
       <c r="D466" t="b">
         <v>0</v>
       </c>
-      <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
-      <c r="G466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -11180,9 +9785,6 @@
       <c r="D467" t="b">
         <v>0</v>
       </c>
-      <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
-      <c r="G467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -11203,9 +9805,6 @@
       <c r="D468" t="b">
         <v>0</v>
       </c>
-      <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
-      <c r="G468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -11226,9 +9825,6 @@
       <c r="D469" t="b">
         <v>0</v>
       </c>
-      <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
-      <c r="G469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -11249,9 +9845,6 @@
       <c r="D470" t="b">
         <v>0</v>
       </c>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
-      <c r="G470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -11272,9 +9865,6 @@
       <c r="D471" t="b">
         <v>0</v>
       </c>
-      <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
-      <c r="G471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -11295,9 +9885,6 @@
       <c r="D472" t="b">
         <v>0</v>
       </c>
-      <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
-      <c r="G472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -11318,9 +9905,6 @@
       <c r="D473" t="b">
         <v>1</v>
       </c>
-      <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
-      <c r="G473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -11341,9 +9925,6 @@
       <c r="D474" t="b">
         <v>1</v>
       </c>
-      <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
-      <c r="G474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -11364,9 +9945,6 @@
       <c r="D475" t="b">
         <v>1</v>
       </c>
-      <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
-      <c r="G475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -11387,9 +9965,6 @@
       <c r="D476" t="b">
         <v>1</v>
       </c>
-      <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
-      <c r="G476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -11410,9 +9985,6 @@
       <c r="D477" t="b">
         <v>1</v>
       </c>
-      <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
-      <c r="G477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -11433,9 +10005,6 @@
       <c r="D478" t="b">
         <v>0</v>
       </c>
-      <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
-      <c r="G478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -11456,9 +10025,6 @@
       <c r="D479" t="b">
         <v>0</v>
       </c>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -11479,9 +10045,6 @@
       <c r="D480" t="b">
         <v>0</v>
       </c>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -11502,9 +10065,6 @@
       <c r="D481" t="b">
         <v>0</v>
       </c>
-      <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
-      <c r="G481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -11525,9 +10085,6 @@
       <c r="D482" t="b">
         <v>0</v>
       </c>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
-      <c r="G482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -11548,9 +10105,6 @@
       <c r="D483" t="b">
         <v>0</v>
       </c>
-      <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
-      <c r="G483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -11571,9 +10125,6 @@
       <c r="D484" t="b">
         <v>0</v>
       </c>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -11594,9 +10145,6 @@
       <c r="D485" t="b">
         <v>1</v>
       </c>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -11617,9 +10165,6 @@
       <c r="D486" t="b">
         <v>0</v>
       </c>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
-      <c r="G486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -11640,9 +10185,6 @@
       <c r="D487" t="b">
         <v>0</v>
       </c>
-      <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
-      <c r="G487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -11663,9 +10205,6 @@
       <c r="D488" t="b">
         <v>0</v>
       </c>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
-      <c r="G488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -11686,9 +10225,6 @@
       <c r="D489" t="b">
         <v>0</v>
       </c>
-      <c r="E489" t="inlineStr"/>
-      <c r="F489" t="inlineStr"/>
-      <c r="G489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -11709,9 +10245,6 @@
       <c r="D490" t="b">
         <v>0</v>
       </c>
-      <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
-      <c r="G490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -11732,9 +10265,6 @@
       <c r="D491" t="b">
         <v>0</v>
       </c>
-      <c r="E491" t="inlineStr"/>
-      <c r="F491" t="inlineStr"/>
-      <c r="G491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -11755,9 +10285,6 @@
       <c r="D492" t="b">
         <v>0</v>
       </c>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
-      <c r="G492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -11778,9 +10305,6 @@
       <c r="D493" t="b">
         <v>1</v>
       </c>
-      <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
-      <c r="G493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -11801,9 +10325,6 @@
       <c r="D494" t="b">
         <v>1</v>
       </c>
-      <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
-      <c r="G494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -11824,9 +10345,6 @@
       <c r="D495" t="b">
         <v>0</v>
       </c>
-      <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
-      <c r="G495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -11847,9 +10365,6 @@
       <c r="D496" t="b">
         <v>0</v>
       </c>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
-      <c r="G496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -11870,9 +10385,6 @@
       <c r="D497" t="b">
         <v>0</v>
       </c>
-      <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
-      <c r="G497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -11893,9 +10405,6 @@
       <c r="D498" t="b">
         <v>0</v>
       </c>
-      <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
-      <c r="G498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -11916,9 +10425,6 @@
       <c r="D499" t="b">
         <v>0</v>
       </c>
-      <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
-      <c r="G499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -11939,9 +10445,6 @@
       <c r="D500" t="b">
         <v>0</v>
       </c>
-      <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
-      <c r="G500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -11962,9 +10465,6 @@
       <c r="D501" t="b">
         <v>0</v>
       </c>
-      <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -11985,9 +10485,6 @@
       <c r="D502" t="b">
         <v>0</v>
       </c>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -12008,9 +10505,6 @@
       <c r="D503" t="b">
         <v>0</v>
       </c>
-      <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
-      <c r="G503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -12031,9 +10525,6 @@
       <c r="D504" t="b">
         <v>0</v>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
-      <c r="G504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -12054,9 +10545,6 @@
       <c r="D505" t="b">
         <v>0</v>
       </c>
-      <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
-      <c r="G505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -12077,9 +10565,6 @@
       <c r="D506" t="b">
         <v>0</v>
       </c>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
-      <c r="G506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -12100,9 +10585,6 @@
       <c r="D507" t="b">
         <v>0</v>
       </c>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
-      <c r="G507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -12123,9 +10605,6 @@
       <c r="D508" t="b">
         <v>0</v>
       </c>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
-      <c r="G508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -12146,9 +10625,6 @@
       <c r="D509" t="b">
         <v>0</v>
       </c>
-      <c r="E509" t="inlineStr"/>
-      <c r="F509" t="inlineStr"/>
-      <c r="G509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -12169,9 +10645,6 @@
       <c r="D510" t="b">
         <v>1</v>
       </c>
-      <c r="E510" t="inlineStr"/>
-      <c r="F510" t="inlineStr"/>
-      <c r="G510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -12192,9 +10665,6 @@
       <c r="D511" t="b">
         <v>1</v>
       </c>
-      <c r="E511" t="inlineStr"/>
-      <c r="F511" t="inlineStr"/>
-      <c r="G511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -12215,9 +10685,6 @@
       <c r="D512" t="b">
         <v>0</v>
       </c>
-      <c r="E512" t="inlineStr"/>
-      <c r="F512" t="inlineStr"/>
-      <c r="G512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -12238,9 +10705,6 @@
       <c r="D513" t="b">
         <v>0</v>
       </c>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
-      <c r="G513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -12261,9 +10725,6 @@
       <c r="D514" t="b">
         <v>0</v>
       </c>
-      <c r="E514" t="inlineStr"/>
-      <c r="F514" t="inlineStr"/>
-      <c r="G514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -12284,9 +10745,6 @@
       <c r="D515" t="b">
         <v>0</v>
       </c>
-      <c r="E515" t="inlineStr"/>
-      <c r="F515" t="inlineStr"/>
-      <c r="G515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -12307,9 +10765,6 @@
       <c r="D516" t="b">
         <v>0</v>
       </c>
-      <c r="E516" t="inlineStr"/>
-      <c r="F516" t="inlineStr"/>
-      <c r="G516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -12330,9 +10785,6 @@
       <c r="D517" t="b">
         <v>0</v>
       </c>
-      <c r="E517" t="inlineStr"/>
-      <c r="F517" t="inlineStr"/>
-      <c r="G517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -12353,9 +10805,6 @@
       <c r="D518" t="b">
         <v>0</v>
       </c>
-      <c r="E518" t="inlineStr"/>
-      <c r="F518" t="inlineStr"/>
-      <c r="G518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -12376,9 +10825,6 @@
       <c r="D519" t="b">
         <v>1</v>
       </c>
-      <c r="E519" t="inlineStr"/>
-      <c r="F519" t="inlineStr"/>
-      <c r="G519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -12399,9 +10845,6 @@
       <c r="D520" t="b">
         <v>1</v>
       </c>
-      <c r="E520" t="inlineStr"/>
-      <c r="F520" t="inlineStr"/>
-      <c r="G520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -12422,9 +10865,6 @@
       <c r="D521" t="b">
         <v>0</v>
       </c>
-      <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
-      <c r="G521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -12445,9 +10885,6 @@
       <c r="D522" t="b">
         <v>0</v>
       </c>
-      <c r="E522" t="inlineStr"/>
-      <c r="F522" t="inlineStr"/>
-      <c r="G522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -12468,9 +10905,6 @@
       <c r="D523" t="b">
         <v>0</v>
       </c>
-      <c r="E523" t="inlineStr"/>
-      <c r="F523" t="inlineStr"/>
-      <c r="G523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -12491,9 +10925,6 @@
       <c r="D524" t="b">
         <v>0</v>
       </c>
-      <c r="E524" t="inlineStr"/>
-      <c r="F524" t="inlineStr"/>
-      <c r="G524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -12514,9 +10945,6 @@
       <c r="D525" t="b">
         <v>0</v>
       </c>
-      <c r="E525" t="inlineStr"/>
-      <c r="F525" t="inlineStr"/>
-      <c r="G525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -12537,9 +10965,6 @@
       <c r="D526" t="b">
         <v>0</v>
       </c>
-      <c r="E526" t="inlineStr"/>
-      <c r="F526" t="inlineStr"/>
-      <c r="G526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -12560,9 +10985,6 @@
       <c r="D527" t="b">
         <v>0</v>
       </c>
-      <c r="E527" t="inlineStr"/>
-      <c r="F527" t="inlineStr"/>
-      <c r="G527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -12583,9 +11005,6 @@
       <c r="D528" t="b">
         <v>1</v>
       </c>
-      <c r="E528" t="inlineStr"/>
-      <c r="F528" t="inlineStr"/>
-      <c r="G528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -12606,9 +11025,6 @@
       <c r="D529" t="b">
         <v>1</v>
       </c>
-      <c r="E529" t="inlineStr"/>
-      <c r="F529" t="inlineStr"/>
-      <c r="G529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -12629,9 +11045,6 @@
       <c r="D530" t="b">
         <v>1</v>
       </c>
-      <c r="E530" t="inlineStr"/>
-      <c r="F530" t="inlineStr"/>
-      <c r="G530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -12652,9 +11065,6 @@
       <c r="D531" t="b">
         <v>0</v>
       </c>
-      <c r="E531" t="inlineStr"/>
-      <c r="F531" t="inlineStr"/>
-      <c r="G531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -12675,9 +11085,6 @@
       <c r="D532" t="b">
         <v>0</v>
       </c>
-      <c r="E532" t="inlineStr"/>
-      <c r="F532" t="inlineStr"/>
-      <c r="G532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -12698,9 +11105,6 @@
       <c r="D533" t="b">
         <v>0</v>
       </c>
-      <c r="E533" t="inlineStr"/>
-      <c r="F533" t="inlineStr"/>
-      <c r="G533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -12721,9 +11125,6 @@
       <c r="D534" t="b">
         <v>0</v>
       </c>
-      <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
-      <c r="G534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -12744,9 +11145,6 @@
       <c r="D535" t="b">
         <v>0</v>
       </c>
-      <c r="E535" t="inlineStr"/>
-      <c r="F535" t="inlineStr"/>
-      <c r="G535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -12767,9 +11165,6 @@
       <c r="D536" t="b">
         <v>0</v>
       </c>
-      <c r="E536" t="inlineStr"/>
-      <c r="F536" t="inlineStr"/>
-      <c r="G536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -12790,9 +11185,6 @@
       <c r="D537" t="b">
         <v>0</v>
       </c>
-      <c r="E537" t="inlineStr"/>
-      <c r="F537" t="inlineStr"/>
-      <c r="G537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -12813,9 +11205,6 @@
       <c r="D538" t="b">
         <v>0</v>
       </c>
-      <c r="E538" t="inlineStr"/>
-      <c r="F538" t="inlineStr"/>
-      <c r="G538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -12836,9 +11225,6 @@
       <c r="D539" t="b">
         <v>0</v>
       </c>
-      <c r="E539" t="inlineStr"/>
-      <c r="F539" t="inlineStr"/>
-      <c r="G539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -12859,9 +11245,6 @@
       <c r="D540" t="b">
         <v>0</v>
       </c>
-      <c r="E540" t="inlineStr"/>
-      <c r="F540" t="inlineStr"/>
-      <c r="G540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -12882,9 +11265,6 @@
       <c r="D541" t="b">
         <v>0</v>
       </c>
-      <c r="E541" t="inlineStr"/>
-      <c r="F541" t="inlineStr"/>
-      <c r="G541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -12905,9 +11285,6 @@
       <c r="D542" t="b">
         <v>0</v>
       </c>
-      <c r="E542" t="inlineStr"/>
-      <c r="F542" t="inlineStr"/>
-      <c r="G542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -12928,9 +11305,6 @@
       <c r="D543" t="b">
         <v>0</v>
       </c>
-      <c r="E543" t="inlineStr"/>
-      <c r="F543" t="inlineStr"/>
-      <c r="G543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -12951,9 +11325,6 @@
       <c r="D544" t="b">
         <v>0</v>
       </c>
-      <c r="E544" t="inlineStr"/>
-      <c r="F544" t="inlineStr"/>
-      <c r="G544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -12974,9 +11345,6 @@
       <c r="D545" t="b">
         <v>0</v>
       </c>
-      <c r="E545" t="inlineStr"/>
-      <c r="F545" t="inlineStr"/>
-      <c r="G545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -12997,9 +11365,6 @@
       <c r="D546" t="b">
         <v>1</v>
       </c>
-      <c r="E546" t="inlineStr"/>
-      <c r="F546" t="inlineStr"/>
-      <c r="G546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -13020,9 +11385,6 @@
       <c r="D547" t="b">
         <v>1</v>
       </c>
-      <c r="E547" t="inlineStr"/>
-      <c r="F547" t="inlineStr"/>
-      <c r="G547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -13043,9 +11405,6 @@
       <c r="D548" t="b">
         <v>0</v>
       </c>
-      <c r="E548" t="inlineStr"/>
-      <c r="F548" t="inlineStr"/>
-      <c r="G548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -13066,9 +11425,6 @@
       <c r="D549" t="b">
         <v>0</v>
       </c>
-      <c r="E549" t="inlineStr"/>
-      <c r="F549" t="inlineStr"/>
-      <c r="G549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -13089,9 +11445,6 @@
       <c r="D550" t="b">
         <v>0</v>
       </c>
-      <c r="E550" t="inlineStr"/>
-      <c r="F550" t="inlineStr"/>
-      <c r="G550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -13112,9 +11465,6 @@
       <c r="D551" t="b">
         <v>0</v>
       </c>
-      <c r="E551" t="inlineStr"/>
-      <c r="F551" t="inlineStr"/>
-      <c r="G551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -13135,9 +11485,6 @@
       <c r="D552" t="b">
         <v>0</v>
       </c>
-      <c r="E552" t="inlineStr"/>
-      <c r="F552" t="inlineStr"/>
-      <c r="G552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -13158,9 +11505,6 @@
       <c r="D553" t="b">
         <v>0</v>
       </c>
-      <c r="E553" t="inlineStr"/>
-      <c r="F553" t="inlineStr"/>
-      <c r="G553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -13181,9 +11525,6 @@
       <c r="D554" t="b">
         <v>0</v>
       </c>
-      <c r="E554" t="inlineStr"/>
-      <c r="F554" t="inlineStr"/>
-      <c r="G554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -13204,9 +11545,6 @@
       <c r="D555" t="b">
         <v>0</v>
       </c>
-      <c r="E555" t="inlineStr"/>
-      <c r="F555" t="inlineStr"/>
-      <c r="G555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -13227,9 +11565,6 @@
       <c r="D556" t="b">
         <v>0</v>
       </c>
-      <c r="E556" t="inlineStr"/>
-      <c r="F556" t="inlineStr"/>
-      <c r="G556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -13250,9 +11585,6 @@
       <c r="D557" t="b">
         <v>0</v>
       </c>
-      <c r="E557" t="inlineStr"/>
-      <c r="F557" t="inlineStr"/>
-      <c r="G557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -13273,9 +11605,6 @@
       <c r="D558" t="b">
         <v>0</v>
       </c>
-      <c r="E558" t="inlineStr"/>
-      <c r="F558" t="inlineStr"/>
-      <c r="G558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -13296,9 +11625,6 @@
       <c r="D559" t="b">
         <v>0</v>
       </c>
-      <c r="E559" t="inlineStr"/>
-      <c r="F559" t="inlineStr"/>
-      <c r="G559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -13319,9 +11645,6 @@
       <c r="D560" t="b">
         <v>0</v>
       </c>
-      <c r="E560" t="inlineStr"/>
-      <c r="F560" t="inlineStr"/>
-      <c r="G560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -13342,9 +11665,6 @@
       <c r="D561" t="b">
         <v>0</v>
       </c>
-      <c r="E561" t="inlineStr"/>
-      <c r="F561" t="inlineStr"/>
-      <c r="G561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -13365,9 +11685,6 @@
       <c r="D562" t="b">
         <v>0</v>
       </c>
-      <c r="E562" t="inlineStr"/>
-      <c r="F562" t="inlineStr"/>
-      <c r="G562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -13388,9 +11705,6 @@
       <c r="D563" t="b">
         <v>1</v>
       </c>
-      <c r="E563" t="inlineStr"/>
-      <c r="F563" t="inlineStr"/>
-      <c r="G563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -13411,9 +11725,6 @@
       <c r="D564" t="b">
         <v>1</v>
       </c>
-      <c r="E564" t="inlineStr"/>
-      <c r="F564" t="inlineStr"/>
-      <c r="G564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -13434,9 +11745,6 @@
       <c r="D565" t="b">
         <v>1</v>
       </c>
-      <c r="E565" t="inlineStr"/>
-      <c r="F565" t="inlineStr"/>
-      <c r="G565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -13457,9 +11765,6 @@
       <c r="D566" t="b">
         <v>0</v>
       </c>
-      <c r="E566" t="inlineStr"/>
-      <c r="F566" t="inlineStr"/>
-      <c r="G566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -13480,9 +11785,6 @@
       <c r="D567" t="b">
         <v>0</v>
       </c>
-      <c r="E567" t="inlineStr"/>
-      <c r="F567" t="inlineStr"/>
-      <c r="G567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -13503,9 +11805,6 @@
       <c r="D568" t="b">
         <v>0</v>
       </c>
-      <c r="E568" t="inlineStr"/>
-      <c r="F568" t="inlineStr"/>
-      <c r="G568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -13526,9 +11825,6 @@
       <c r="D569" t="b">
         <v>0</v>
       </c>
-      <c r="E569" t="inlineStr"/>
-      <c r="F569" t="inlineStr"/>
-      <c r="G569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -13549,9 +11845,6 @@
       <c r="D570" t="b">
         <v>0</v>
       </c>
-      <c r="E570" t="inlineStr"/>
-      <c r="F570" t="inlineStr"/>
-      <c r="G570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -13572,9 +11865,6 @@
       <c r="D571" t="b">
         <v>0</v>
       </c>
-      <c r="E571" t="inlineStr"/>
-      <c r="F571" t="inlineStr"/>
-      <c r="G571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -13595,9 +11885,6 @@
       <c r="D572" t="b">
         <v>0</v>
       </c>
-      <c r="E572" t="inlineStr"/>
-      <c r="F572" t="inlineStr"/>
-      <c r="G572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -13618,9 +11905,6 @@
       <c r="D573" t="b">
         <v>0</v>
       </c>
-      <c r="E573" t="inlineStr"/>
-      <c r="F573" t="inlineStr"/>
-      <c r="G573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -13641,9 +11925,6 @@
       <c r="D574" t="b">
         <v>0</v>
       </c>
-      <c r="E574" t="inlineStr"/>
-      <c r="F574" t="inlineStr"/>
-      <c r="G574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -13664,9 +11945,6 @@
       <c r="D575" t="b">
         <v>0</v>
       </c>
-      <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr"/>
-      <c r="G575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -13687,9 +11965,6 @@
       <c r="D576" t="b">
         <v>0</v>
       </c>
-      <c r="E576" t="inlineStr"/>
-      <c r="F576" t="inlineStr"/>
-      <c r="G576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -13710,9 +11985,6 @@
       <c r="D577" t="b">
         <v>0</v>
       </c>
-      <c r="E577" t="inlineStr"/>
-      <c r="F577" t="inlineStr"/>
-      <c r="G577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -13733,9 +12005,6 @@
       <c r="D578" t="b">
         <v>0</v>
       </c>
-      <c r="E578" t="inlineStr"/>
-      <c r="F578" t="inlineStr"/>
-      <c r="G578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -13756,9 +12025,6 @@
       <c r="D579" t="b">
         <v>0</v>
       </c>
-      <c r="E579" t="inlineStr"/>
-      <c r="F579" t="inlineStr"/>
-      <c r="G579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -13779,9 +12045,6 @@
       <c r="D580" t="b">
         <v>0</v>
       </c>
-      <c r="E580" t="inlineStr"/>
-      <c r="F580" t="inlineStr"/>
-      <c r="G580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -13802,9 +12065,6 @@
       <c r="D581" t="b">
         <v>0</v>
       </c>
-      <c r="E581" t="inlineStr"/>
-      <c r="F581" t="inlineStr"/>
-      <c r="G581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -13825,9 +12085,6 @@
       <c r="D582" t="b">
         <v>1</v>
       </c>
-      <c r="E582" t="inlineStr"/>
-      <c r="F582" t="inlineStr"/>
-      <c r="G582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -13848,9 +12105,6 @@
       <c r="D583" t="b">
         <v>1</v>
       </c>
-      <c r="E583" t="inlineStr"/>
-      <c r="F583" t="inlineStr"/>
-      <c r="G583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -13871,9 +12125,6 @@
       <c r="D584" t="b">
         <v>1</v>
       </c>
-      <c r="E584" t="inlineStr"/>
-      <c r="F584" t="inlineStr"/>
-      <c r="G584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -13894,9 +12145,6 @@
       <c r="D585" t="b">
         <v>1</v>
       </c>
-      <c r="E585" t="inlineStr"/>
-      <c r="F585" t="inlineStr"/>
-      <c r="G585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -13917,9 +12165,6 @@
       <c r="D586" t="b">
         <v>1</v>
       </c>
-      <c r="E586" t="inlineStr"/>
-      <c r="F586" t="inlineStr"/>
-      <c r="G586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -13940,9 +12185,6 @@
       <c r="D587" t="b">
         <v>0</v>
       </c>
-      <c r="E587" t="inlineStr"/>
-      <c r="F587" t="inlineStr"/>
-      <c r="G587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -13963,9 +12205,6 @@
       <c r="D588" t="b">
         <v>0</v>
       </c>
-      <c r="E588" t="inlineStr"/>
-      <c r="F588" t="inlineStr"/>
-      <c r="G588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -13986,9 +12225,6 @@
       <c r="D589" t="b">
         <v>0</v>
       </c>
-      <c r="E589" t="inlineStr"/>
-      <c r="F589" t="inlineStr"/>
-      <c r="G589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -14009,9 +12245,6 @@
       <c r="D590" t="b">
         <v>0</v>
       </c>
-      <c r="E590" t="inlineStr"/>
-      <c r="F590" t="inlineStr"/>
-      <c r="G590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -14032,9 +12265,6 @@
       <c r="D591" t="b">
         <v>0</v>
       </c>
-      <c r="E591" t="inlineStr"/>
-      <c r="F591" t="inlineStr"/>
-      <c r="G591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -14049,15 +12279,12 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Ye</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D592" t="b">
         <v>0</v>
       </c>
-      <c r="E592" t="inlineStr"/>
-      <c r="F592" t="inlineStr"/>
-      <c r="G592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -14078,9 +12305,6 @@
       <c r="D593" t="b">
         <v>0</v>
       </c>
-      <c r="E593" t="inlineStr"/>
-      <c r="F593" t="inlineStr"/>
-      <c r="G593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -14101,9 +12325,6 @@
       <c r="D594" t="b">
         <v>0</v>
       </c>
-      <c r="E594" t="inlineStr"/>
-      <c r="F594" t="inlineStr"/>
-      <c r="G594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -14124,9 +12345,6 @@
       <c r="D595" t="b">
         <v>0</v>
       </c>
-      <c r="E595" t="inlineStr"/>
-      <c r="F595" t="inlineStr"/>
-      <c r="G595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -14147,9 +12365,6 @@
       <c r="D596" t="b">
         <v>0</v>
       </c>
-      <c r="E596" t="inlineStr"/>
-      <c r="F596" t="inlineStr"/>
-      <c r="G596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -14170,9 +12385,6 @@
       <c r="D597" t="b">
         <v>0</v>
       </c>
-      <c r="E597" t="inlineStr"/>
-      <c r="F597" t="inlineStr"/>
-      <c r="G597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -14193,9 +12405,6 @@
       <c r="D598" t="b">
         <v>0</v>
       </c>
-      <c r="E598" t="inlineStr"/>
-      <c r="F598" t="inlineStr"/>
-      <c r="G598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -14216,9 +12425,6 @@
       <c r="D599" t="b">
         <v>0</v>
       </c>
-      <c r="E599" t="inlineStr"/>
-      <c r="F599" t="inlineStr"/>
-      <c r="G599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -14239,9 +12445,6 @@
       <c r="D600" t="b">
         <v>0</v>
       </c>
-      <c r="E600" t="inlineStr"/>
-      <c r="F600" t="inlineStr"/>
-      <c r="G600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -14262,9 +12465,6 @@
       <c r="D601" t="b">
         <v>0</v>
       </c>
-      <c r="E601" t="inlineStr"/>
-      <c r="F601" t="inlineStr"/>
-      <c r="G601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -14285,9 +12485,6 @@
       <c r="D602" t="b">
         <v>1</v>
       </c>
-      <c r="E602" t="inlineStr"/>
-      <c r="F602" t="inlineStr"/>
-      <c r="G602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -14308,9 +12505,6 @@
       <c r="D603" t="b">
         <v>0</v>
       </c>
-      <c r="E603" t="inlineStr"/>
-      <c r="F603" t="inlineStr"/>
-      <c r="G603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -14331,9 +12525,6 @@
       <c r="D604" t="b">
         <v>0</v>
       </c>
-      <c r="E604" t="inlineStr"/>
-      <c r="F604" t="inlineStr"/>
-      <c r="G604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -14354,9 +12545,6 @@
       <c r="D605" t="b">
         <v>0</v>
       </c>
-      <c r="E605" t="inlineStr"/>
-      <c r="F605" t="inlineStr"/>
-      <c r="G605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -14377,9 +12565,6 @@
       <c r="D606" t="b">
         <v>0</v>
       </c>
-      <c r="E606" t="inlineStr"/>
-      <c r="F606" t="inlineStr"/>
-      <c r="G606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -14400,9 +12585,6 @@
       <c r="D607" t="b">
         <v>0</v>
       </c>
-      <c r="E607" t="inlineStr"/>
-      <c r="F607" t="inlineStr"/>
-      <c r="G607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -14423,9 +12605,6 @@
       <c r="D608" t="b">
         <v>0</v>
       </c>
-      <c r="E608" t="inlineStr"/>
-      <c r="F608" t="inlineStr"/>
-      <c r="G608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -14446,9 +12625,6 @@
       <c r="D609" t="b">
         <v>0</v>
       </c>
-      <c r="E609" t="inlineStr"/>
-      <c r="F609" t="inlineStr"/>
-      <c r="G609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -14469,9 +12645,6 @@
       <c r="D610" t="b">
         <v>0</v>
       </c>
-      <c r="E610" t="inlineStr"/>
-      <c r="F610" t="inlineStr"/>
-      <c r="G610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -14492,9 +12665,6 @@
       <c r="D611" t="b">
         <v>1</v>
       </c>
-      <c r="E611" t="inlineStr"/>
-      <c r="F611" t="inlineStr"/>
-      <c r="G611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -14515,9 +12685,6 @@
       <c r="D612" t="b">
         <v>0</v>
       </c>
-      <c r="E612" t="inlineStr"/>
-      <c r="F612" t="inlineStr"/>
-      <c r="G612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -14538,9 +12705,6 @@
       <c r="D613" t="b">
         <v>0</v>
       </c>
-      <c r="E613" t="inlineStr"/>
-      <c r="F613" t="inlineStr"/>
-      <c r="G613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -14561,9 +12725,6 @@
       <c r="D614" t="b">
         <v>0</v>
       </c>
-      <c r="E614" t="inlineStr"/>
-      <c r="F614" t="inlineStr"/>
-      <c r="G614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -14584,9 +12745,6 @@
       <c r="D615" t="b">
         <v>0</v>
       </c>
-      <c r="E615" t="inlineStr"/>
-      <c r="F615" t="inlineStr"/>
-      <c r="G615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -14607,9 +12765,6 @@
       <c r="D616" t="b">
         <v>0</v>
       </c>
-      <c r="E616" t="inlineStr"/>
-      <c r="F616" t="inlineStr"/>
-      <c r="G616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -14630,9 +12785,6 @@
       <c r="D617" t="b">
         <v>0</v>
       </c>
-      <c r="E617" t="inlineStr"/>
-      <c r="F617" t="inlineStr"/>
-      <c r="G617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -14653,9 +12805,6 @@
       <c r="D618" t="b">
         <v>0</v>
       </c>
-      <c r="E618" t="inlineStr"/>
-      <c r="F618" t="inlineStr"/>
-      <c r="G618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -14676,9 +12825,6 @@
       <c r="D619" t="b">
         <v>1</v>
       </c>
-      <c r="E619" t="inlineStr"/>
-      <c r="F619" t="inlineStr"/>
-      <c r="G619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -14699,9 +12845,6 @@
       <c r="D620" t="b">
         <v>1</v>
       </c>
-      <c r="E620" t="inlineStr"/>
-      <c r="F620" t="inlineStr"/>
-      <c r="G620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -14722,9 +12865,6 @@
       <c r="D621" t="b">
         <v>1</v>
       </c>
-      <c r="E621" t="inlineStr"/>
-      <c r="F621" t="inlineStr"/>
-      <c r="G621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -14745,9 +12885,6 @@
       <c r="D622" t="b">
         <v>1</v>
       </c>
-      <c r="E622" t="inlineStr"/>
-      <c r="F622" t="inlineStr"/>
-      <c r="G622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -14768,9 +12905,6 @@
       <c r="D623" t="b">
         <v>1</v>
       </c>
-      <c r="E623" t="inlineStr"/>
-      <c r="F623" t="inlineStr"/>
-      <c r="G623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -14791,9 +12925,6 @@
       <c r="D624" t="b">
         <v>0</v>
       </c>
-      <c r="E624" t="inlineStr"/>
-      <c r="F624" t="inlineStr"/>
-      <c r="G624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -14814,9 +12945,6 @@
       <c r="D625" t="b">
         <v>0</v>
       </c>
-      <c r="E625" t="inlineStr"/>
-      <c r="F625" t="inlineStr"/>
-      <c r="G625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -14837,9 +12965,6 @@
       <c r="D626" t="b">
         <v>0</v>
       </c>
-      <c r="E626" t="inlineStr"/>
-      <c r="F626" t="inlineStr"/>
-      <c r="G626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -14860,9 +12985,6 @@
       <c r="D627" t="b">
         <v>0</v>
       </c>
-      <c r="E627" t="inlineStr"/>
-      <c r="F627" t="inlineStr"/>
-      <c r="G627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -14883,9 +13005,6 @@
       <c r="D628" t="b">
         <v>0</v>
       </c>
-      <c r="E628" t="inlineStr"/>
-      <c r="F628" t="inlineStr"/>
-      <c r="G628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -14906,9 +13025,6 @@
       <c r="D629" t="b">
         <v>0</v>
       </c>
-      <c r="E629" t="inlineStr"/>
-      <c r="F629" t="inlineStr"/>
-      <c r="G629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -14929,9 +13045,6 @@
       <c r="D630" t="b">
         <v>0</v>
       </c>
-      <c r="E630" t="inlineStr"/>
-      <c r="F630" t="inlineStr"/>
-      <c r="G630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -14952,9 +13065,6 @@
       <c r="D631" t="b">
         <v>0</v>
       </c>
-      <c r="E631" t="inlineStr"/>
-      <c r="F631" t="inlineStr"/>
-      <c r="G631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -14975,9 +13085,6 @@
       <c r="D632" t="b">
         <v>0</v>
       </c>
-      <c r="E632" t="inlineStr"/>
-      <c r="F632" t="inlineStr"/>
-      <c r="G632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -14998,9 +13105,6 @@
       <c r="D633" t="b">
         <v>0</v>
       </c>
-      <c r="E633" t="inlineStr"/>
-      <c r="F633" t="inlineStr"/>
-      <c r="G633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -15021,9 +13125,6 @@
       <c r="D634" t="b">
         <v>0</v>
       </c>
-      <c r="E634" t="inlineStr"/>
-      <c r="F634" t="inlineStr"/>
-      <c r="G634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -15044,9 +13145,6 @@
       <c r="D635" t="b">
         <v>0</v>
       </c>
-      <c r="E635" t="inlineStr"/>
-      <c r="F635" t="inlineStr"/>
-      <c r="G635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -15067,9 +13165,6 @@
       <c r="D636" t="b">
         <v>0</v>
       </c>
-      <c r="E636" t="inlineStr"/>
-      <c r="F636" t="inlineStr"/>
-      <c r="G636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -15090,9 +13185,6 @@
       <c r="D637" t="b">
         <v>0</v>
       </c>
-      <c r="E637" t="inlineStr"/>
-      <c r="F637" t="inlineStr"/>
-      <c r="G637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -15113,9 +13205,6 @@
       <c r="D638" t="b">
         <v>0</v>
       </c>
-      <c r="E638" t="inlineStr"/>
-      <c r="F638" t="inlineStr"/>
-      <c r="G638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -15136,9 +13225,6 @@
       <c r="D639" t="b">
         <v>1</v>
       </c>
-      <c r="E639" t="inlineStr"/>
-      <c r="F639" t="inlineStr"/>
-      <c r="G639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -15159,9 +13245,6 @@
       <c r="D640" t="b">
         <v>1</v>
       </c>
-      <c r="E640" t="inlineStr"/>
-      <c r="F640" t="inlineStr"/>
-      <c r="G640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -15182,9 +13265,6 @@
       <c r="D641" t="b">
         <v>1</v>
       </c>
-      <c r="E641" t="inlineStr"/>
-      <c r="F641" t="inlineStr"/>
-      <c r="G641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -15205,9 +13285,6 @@
       <c r="D642" t="b">
         <v>1</v>
       </c>
-      <c r="E642" t="inlineStr"/>
-      <c r="F642" t="inlineStr"/>
-      <c r="G642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -15228,9 +13305,6 @@
       <c r="D643" t="b">
         <v>1</v>
       </c>
-      <c r="E643" t="inlineStr"/>
-      <c r="F643" t="inlineStr"/>
-      <c r="G643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -15251,9 +13325,6 @@
       <c r="D644" t="b">
         <v>0</v>
       </c>
-      <c r="E644" t="inlineStr"/>
-      <c r="F644" t="inlineStr"/>
-      <c r="G644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -15274,9 +13345,6 @@
       <c r="D645" t="b">
         <v>0</v>
       </c>
-      <c r="E645" t="inlineStr"/>
-      <c r="F645" t="inlineStr"/>
-      <c r="G645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -15297,9 +13365,6 @@
       <c r="D646" t="b">
         <v>0</v>
       </c>
-      <c r="E646" t="inlineStr"/>
-      <c r="F646" t="inlineStr"/>
-      <c r="G646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -15320,9 +13385,6 @@
       <c r="D647" t="b">
         <v>0</v>
       </c>
-      <c r="E647" t="inlineStr"/>
-      <c r="F647" t="inlineStr"/>
-      <c r="G647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -15343,9 +13405,6 @@
       <c r="D648" t="b">
         <v>0</v>
       </c>
-      <c r="E648" t="inlineStr"/>
-      <c r="F648" t="inlineStr"/>
-      <c r="G648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -15366,9 +13425,6 @@
       <c r="D649" t="b">
         <v>0</v>
       </c>
-      <c r="E649" t="inlineStr"/>
-      <c r="F649" t="inlineStr"/>
-      <c r="G649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -15389,9 +13445,6 @@
       <c r="D650" t="b">
         <v>0</v>
       </c>
-      <c r="E650" t="inlineStr"/>
-      <c r="F650" t="inlineStr"/>
-      <c r="G650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -15412,9 +13465,6 @@
       <c r="D651" t="b">
         <v>1</v>
       </c>
-      <c r="E651" t="inlineStr"/>
-      <c r="F651" t="inlineStr"/>
-      <c r="G651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -15435,9 +13485,6 @@
       <c r="D652" t="b">
         <v>0</v>
       </c>
-      <c r="E652" t="inlineStr"/>
-      <c r="F652" t="inlineStr"/>
-      <c r="G652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -15458,9 +13505,6 @@
       <c r="D653" t="b">
         <v>0</v>
       </c>
-      <c r="E653" t="inlineStr"/>
-      <c r="F653" t="inlineStr"/>
-      <c r="G653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -15481,9 +13525,6 @@
       <c r="D654" t="b">
         <v>0</v>
       </c>
-      <c r="E654" t="inlineStr"/>
-      <c r="F654" t="inlineStr"/>
-      <c r="G654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -15504,9 +13545,6 @@
       <c r="D655" t="b">
         <v>0</v>
       </c>
-      <c r="E655" t="inlineStr"/>
-      <c r="F655" t="inlineStr"/>
-      <c r="G655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -15527,9 +13565,6 @@
       <c r="D656" t="b">
         <v>0</v>
       </c>
-      <c r="E656" t="inlineStr"/>
-      <c r="F656" t="inlineStr"/>
-      <c r="G656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -15550,9 +13585,6 @@
       <c r="D657" t="b">
         <v>0</v>
       </c>
-      <c r="E657" t="inlineStr"/>
-      <c r="F657" t="inlineStr"/>
-      <c r="G657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -15573,9 +13605,6 @@
       <c r="D658" t="b">
         <v>0</v>
       </c>
-      <c r="E658" t="inlineStr"/>
-      <c r="F658" t="inlineStr"/>
-      <c r="G658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -15596,9 +13625,6 @@
       <c r="D659" t="b">
         <v>1</v>
       </c>
-      <c r="E659" t="inlineStr"/>
-      <c r="F659" t="inlineStr"/>
-      <c r="G659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -15619,9 +13645,6 @@
       <c r="D660" t="b">
         <v>1</v>
       </c>
-      <c r="E660" t="inlineStr"/>
-      <c r="F660" t="inlineStr"/>
-      <c r="G660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -15642,9 +13665,6 @@
       <c r="D661" t="b">
         <v>1</v>
       </c>
-      <c r="E661" t="inlineStr"/>
-      <c r="F661" t="inlineStr"/>
-      <c r="G661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -15665,9 +13685,6 @@
       <c r="D662" t="b">
         <v>1</v>
       </c>
-      <c r="E662" t="inlineStr"/>
-      <c r="F662" t="inlineStr"/>
-      <c r="G662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -15688,9 +13705,6 @@
       <c r="D663" t="b">
         <v>1</v>
       </c>
-      <c r="E663" t="inlineStr"/>
-      <c r="F663" t="inlineStr"/>
-      <c r="G663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -15711,9 +13725,6 @@
       <c r="D664" t="b">
         <v>0</v>
       </c>
-      <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr"/>
-      <c r="G664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -15734,9 +13745,6 @@
       <c r="D665" t="b">
         <v>0</v>
       </c>
-      <c r="E665" t="inlineStr"/>
-      <c r="F665" t="inlineStr"/>
-      <c r="G665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -15757,9 +13765,6 @@
       <c r="D666" t="b">
         <v>0</v>
       </c>
-      <c r="E666" t="inlineStr"/>
-      <c r="F666" t="inlineStr"/>
-      <c r="G666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -15780,9 +13785,6 @@
       <c r="D667" t="b">
         <v>0</v>
       </c>
-      <c r="E667" t="inlineStr"/>
-      <c r="F667" t="inlineStr"/>
-      <c r="G667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -15803,9 +13805,6 @@
       <c r="D668" t="b">
         <v>0</v>
       </c>
-      <c r="E668" t="inlineStr"/>
-      <c r="F668" t="inlineStr"/>
-      <c r="G668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -15826,9 +13825,6 @@
       <c r="D669" t="b">
         <v>0</v>
       </c>
-      <c r="E669" t="inlineStr"/>
-      <c r="F669" t="inlineStr"/>
-      <c r="G669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -15849,9 +13845,6 @@
       <c r="D670" t="b">
         <v>0</v>
       </c>
-      <c r="E670" t="inlineStr"/>
-      <c r="F670" t="inlineStr"/>
-      <c r="G670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -15872,9 +13865,6 @@
       <c r="D671" t="b">
         <v>0</v>
       </c>
-      <c r="E671" t="inlineStr"/>
-      <c r="F671" t="inlineStr"/>
-      <c r="G671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -15895,9 +13885,6 @@
       <c r="D672" t="b">
         <v>0</v>
       </c>
-      <c r="E672" t="inlineStr"/>
-      <c r="F672" t="inlineStr"/>
-      <c r="G672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -15918,9 +13905,6 @@
       <c r="D673" t="b">
         <v>0</v>
       </c>
-      <c r="E673" t="inlineStr"/>
-      <c r="F673" t="inlineStr"/>
-      <c r="G673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -15941,9 +13925,6 @@
       <c r="D674" t="b">
         <v>0</v>
       </c>
-      <c r="E674" t="inlineStr"/>
-      <c r="F674" t="inlineStr"/>
-      <c r="G674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -15964,9 +13945,6 @@
       <c r="D675" t="b">
         <v>0</v>
       </c>
-      <c r="E675" t="inlineStr"/>
-      <c r="F675" t="inlineStr"/>
-      <c r="G675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -15987,9 +13965,6 @@
       <c r="D676" t="b">
         <v>0</v>
       </c>
-      <c r="E676" t="inlineStr"/>
-      <c r="F676" t="inlineStr"/>
-      <c r="G676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -16010,9 +13985,6 @@
       <c r="D677" t="b">
         <v>0</v>
       </c>
-      <c r="E677" t="inlineStr"/>
-      <c r="F677" t="inlineStr"/>
-      <c r="G677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -16033,9 +14005,6 @@
       <c r="D678" t="b">
         <v>0</v>
       </c>
-      <c r="E678" t="inlineStr"/>
-      <c r="F678" t="inlineStr"/>
-      <c r="G678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -16056,9 +14025,6 @@
       <c r="D679" t="b">
         <v>1</v>
       </c>
-      <c r="E679" t="inlineStr"/>
-      <c r="F679" t="inlineStr"/>
-      <c r="G679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -16079,9 +14045,6 @@
       <c r="D680" t="b">
         <v>1</v>
       </c>
-      <c r="E680" t="inlineStr"/>
-      <c r="F680" t="inlineStr"/>
-      <c r="G680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -16102,9 +14065,6 @@
       <c r="D681" t="b">
         <v>1</v>
       </c>
-      <c r="E681" t="inlineStr"/>
-      <c r="F681" t="inlineStr"/>
-      <c r="G681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -16125,9 +14085,6 @@
       <c r="D682" t="b">
         <v>0</v>
       </c>
-      <c r="E682" t="inlineStr"/>
-      <c r="F682" t="inlineStr"/>
-      <c r="G682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -16148,9 +14105,6 @@
       <c r="D683" t="b">
         <v>0</v>
       </c>
-      <c r="E683" t="inlineStr"/>
-      <c r="F683" t="inlineStr"/>
-      <c r="G683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -16171,9 +14125,6 @@
       <c r="D684" t="b">
         <v>0</v>
       </c>
-      <c r="E684" t="inlineStr"/>
-      <c r="F684" t="inlineStr"/>
-      <c r="G684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -16194,9 +14145,6 @@
       <c r="D685" t="b">
         <v>0</v>
       </c>
-      <c r="E685" t="inlineStr"/>
-      <c r="F685" t="inlineStr"/>
-      <c r="G685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -16217,9 +14165,6 @@
       <c r="D686" t="b">
         <v>0</v>
       </c>
-      <c r="E686" t="inlineStr"/>
-      <c r="F686" t="inlineStr"/>
-      <c r="G686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -16240,9 +14185,6 @@
       <c r="D687" t="b">
         <v>0</v>
       </c>
-      <c r="E687" t="inlineStr"/>
-      <c r="F687" t="inlineStr"/>
-      <c r="G687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -16263,9 +14205,6 @@
       <c r="D688" t="b">
         <v>0</v>
       </c>
-      <c r="E688" t="inlineStr"/>
-      <c r="F688" t="inlineStr"/>
-      <c r="G688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -16286,9 +14225,6 @@
       <c r="D689" t="b">
         <v>0</v>
       </c>
-      <c r="E689" t="inlineStr"/>
-      <c r="F689" t="inlineStr"/>
-      <c r="G689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -16309,9 +14245,6 @@
       <c r="D690" t="b">
         <v>0</v>
       </c>
-      <c r="E690" t="inlineStr"/>
-      <c r="F690" t="inlineStr"/>
-      <c r="G690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -16332,9 +14265,6 @@
       <c r="D691" t="b">
         <v>0</v>
       </c>
-      <c r="E691" t="inlineStr"/>
-      <c r="F691" t="inlineStr"/>
-      <c r="G691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -16355,9 +14285,6 @@
       <c r="D692" t="b">
         <v>0</v>
       </c>
-      <c r="E692" t="inlineStr"/>
-      <c r="F692" t="inlineStr"/>
-      <c r="G692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -16378,9 +14305,6 @@
       <c r="D693" t="b">
         <v>0</v>
       </c>
-      <c r="E693" t="inlineStr"/>
-      <c r="F693" t="inlineStr"/>
-      <c r="G693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -16401,9 +14325,6 @@
       <c r="D694" t="b">
         <v>0</v>
       </c>
-      <c r="E694" t="inlineStr"/>
-      <c r="F694" t="inlineStr"/>
-      <c r="G694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -16424,9 +14345,6 @@
       <c r="D695" t="b">
         <v>0</v>
       </c>
-      <c r="E695" t="inlineStr"/>
-      <c r="F695" t="inlineStr"/>
-      <c r="G695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -16447,9 +14365,6 @@
       <c r="D696" t="b">
         <v>1</v>
       </c>
-      <c r="E696" t="inlineStr"/>
-      <c r="F696" t="inlineStr"/>
-      <c r="G696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -16470,9 +14385,6 @@
       <c r="D697" t="b">
         <v>1</v>
       </c>
-      <c r="E697" t="inlineStr"/>
-      <c r="F697" t="inlineStr"/>
-      <c r="G697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -16493,9 +14405,6 @@
       <c r="D698" t="b">
         <v>1</v>
       </c>
-      <c r="E698" t="inlineStr"/>
-      <c r="F698" t="inlineStr"/>
-      <c r="G698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -16516,9 +14425,6 @@
       <c r="D699" t="b">
         <v>1</v>
       </c>
-      <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr"/>
-      <c r="G699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -16539,9 +14445,6 @@
       <c r="D700" t="b">
         <v>1</v>
       </c>
-      <c r="E700" t="inlineStr"/>
-      <c r="F700" t="inlineStr"/>
-      <c r="G700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -16562,9 +14465,6 @@
       <c r="D701" t="b">
         <v>1</v>
       </c>
-      <c r="E701" t="inlineStr"/>
-      <c r="F701" t="inlineStr"/>
-      <c r="G701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -16585,9 +14485,6 @@
       <c r="D702" t="b">
         <v>1</v>
       </c>
-      <c r="E702" t="inlineStr"/>
-      <c r="F702" t="inlineStr"/>
-      <c r="G702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -16608,9 +14505,6 @@
       <c r="D703" t="b">
         <v>1</v>
       </c>
-      <c r="E703" t="inlineStr"/>
-      <c r="F703" t="inlineStr"/>
-      <c r="G703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -16631,9 +14525,6 @@
       <c r="D704" t="b">
         <v>1</v>
       </c>
-      <c r="E704" t="inlineStr"/>
-      <c r="F704" t="inlineStr"/>
-      <c r="G704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -16654,9 +14545,6 @@
       <c r="D705" t="b">
         <v>1</v>
       </c>
-      <c r="E705" t="inlineStr"/>
-      <c r="F705" t="inlineStr"/>
-      <c r="G705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -16677,9 +14565,6 @@
       <c r="D706" t="b">
         <v>1</v>
       </c>
-      <c r="E706" t="inlineStr"/>
-      <c r="F706" t="inlineStr"/>
-      <c r="G706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -16700,9 +14585,6 @@
       <c r="D707" t="b">
         <v>1</v>
       </c>
-      <c r="E707" t="inlineStr"/>
-      <c r="F707" t="inlineStr"/>
-      <c r="G707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -16723,9 +14605,6 @@
       <c r="D708" t="b">
         <v>0</v>
       </c>
-      <c r="E708" t="inlineStr"/>
-      <c r="F708" t="inlineStr"/>
-      <c r="G708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -16746,9 +14625,6 @@
       <c r="D709" t="b">
         <v>0</v>
       </c>
-      <c r="E709" t="inlineStr"/>
-      <c r="F709" t="inlineStr"/>
-      <c r="G709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -16769,9 +14645,6 @@
       <c r="D710" t="b">
         <v>0</v>
       </c>
-      <c r="E710" t="inlineStr"/>
-      <c r="F710" t="inlineStr"/>
-      <c r="G710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -16792,9 +14665,6 @@
       <c r="D711" t="b">
         <v>0</v>
       </c>
-      <c r="E711" t="inlineStr"/>
-      <c r="F711" t="inlineStr"/>
-      <c r="G711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -16815,9 +14685,6 @@
       <c r="D712" t="b">
         <v>0</v>
       </c>
-      <c r="E712" t="inlineStr"/>
-      <c r="F712" t="inlineStr"/>
-      <c r="G712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -16838,9 +14705,6 @@
       <c r="D713" t="b">
         <v>0</v>
       </c>
-      <c r="E713" t="inlineStr"/>
-      <c r="F713" t="inlineStr"/>
-      <c r="G713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -16861,9 +14725,6 @@
       <c r="D714" t="b">
         <v>0</v>
       </c>
-      <c r="E714" t="inlineStr"/>
-      <c r="F714" t="inlineStr"/>
-      <c r="G714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -16884,9 +14745,6 @@
       <c r="D715" t="b">
         <v>1</v>
       </c>
-      <c r="E715" t="inlineStr"/>
-      <c r="F715" t="inlineStr"/>
-      <c r="G715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -16907,9 +14765,6 @@
       <c r="D716" t="b">
         <v>0</v>
       </c>
-      <c r="E716" t="inlineStr"/>
-      <c r="F716" t="inlineStr"/>
-      <c r="G716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -16930,9 +14785,6 @@
       <c r="D717" t="b">
         <v>0</v>
       </c>
-      <c r="E717" t="inlineStr"/>
-      <c r="F717" t="inlineStr"/>
-      <c r="G717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -16953,9 +14805,6 @@
       <c r="D718" t="b">
         <v>0</v>
       </c>
-      <c r="E718" t="inlineStr"/>
-      <c r="F718" t="inlineStr"/>
-      <c r="G718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -16976,9 +14825,6 @@
       <c r="D719" t="b">
         <v>0</v>
       </c>
-      <c r="E719" t="inlineStr"/>
-      <c r="F719" t="inlineStr"/>
-      <c r="G719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -16999,9 +14845,6 @@
       <c r="D720" t="b">
         <v>0</v>
       </c>
-      <c r="E720" t="inlineStr"/>
-      <c r="F720" t="inlineStr"/>
-      <c r="G720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -17022,9 +14865,6 @@
       <c r="D721" t="b">
         <v>0</v>
       </c>
-      <c r="E721" t="inlineStr"/>
-      <c r="F721" t="inlineStr"/>
-      <c r="G721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -17045,9 +14885,6 @@
       <c r="D722" t="b">
         <v>0</v>
       </c>
-      <c r="E722" t="inlineStr"/>
-      <c r="F722" t="inlineStr"/>
-      <c r="G722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -17068,9 +14905,6 @@
       <c r="D723" t="b">
         <v>1</v>
       </c>
-      <c r="E723" t="inlineStr"/>
-      <c r="F723" t="inlineStr"/>
-      <c r="G723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -17091,9 +14925,6 @@
       <c r="D724" t="b">
         <v>1</v>
       </c>
-      <c r="E724" t="inlineStr"/>
-      <c r="F724" t="inlineStr"/>
-      <c r="G724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -17114,9 +14945,6 @@
       <c r="D725" t="b">
         <v>1</v>
       </c>
-      <c r="E725" t="inlineStr"/>
-      <c r="F725" t="inlineStr"/>
-      <c r="G725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -17137,9 +14965,6 @@
       <c r="D726" t="b">
         <v>1</v>
       </c>
-      <c r="E726" t="inlineStr"/>
-      <c r="F726" t="inlineStr"/>
-      <c r="G726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -17160,9 +14985,6 @@
       <c r="D727" t="b">
         <v>1</v>
       </c>
-      <c r="E727" t="inlineStr"/>
-      <c r="F727" t="inlineStr"/>
-      <c r="G727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -17183,9 +15005,6 @@
       <c r="D728" t="b">
         <v>1</v>
       </c>
-      <c r="E728" t="inlineStr"/>
-      <c r="F728" t="inlineStr"/>
-      <c r="G728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -17206,9 +15025,6 @@
       <c r="D729" t="b">
         <v>1</v>
       </c>
-      <c r="E729" t="inlineStr"/>
-      <c r="F729" t="inlineStr"/>
-      <c r="G729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -17229,9 +15045,6 @@
       <c r="D730" t="b">
         <v>1</v>
       </c>
-      <c r="E730" t="inlineStr"/>
-      <c r="F730" t="inlineStr"/>
-      <c r="G730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -17252,9 +15065,6 @@
       <c r="D731" t="b">
         <v>0</v>
       </c>
-      <c r="E731" t="inlineStr"/>
-      <c r="F731" t="inlineStr"/>
-      <c r="G731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -17275,9 +15085,6 @@
       <c r="D732" t="b">
         <v>0</v>
       </c>
-      <c r="E732" t="inlineStr"/>
-      <c r="F732" t="inlineStr"/>
-      <c r="G732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -17298,9 +15105,6 @@
       <c r="D733" t="b">
         <v>0</v>
       </c>
-      <c r="E733" t="inlineStr"/>
-      <c r="F733" t="inlineStr"/>
-      <c r="G733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -17321,9 +15125,6 @@
       <c r="D734" t="b">
         <v>0</v>
       </c>
-      <c r="E734" t="inlineStr"/>
-      <c r="F734" t="inlineStr"/>
-      <c r="G734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -17344,9 +15145,6 @@
       <c r="D735" t="b">
         <v>0</v>
       </c>
-      <c r="E735" t="inlineStr"/>
-      <c r="F735" t="inlineStr"/>
-      <c r="G735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -17367,9 +15165,6 @@
       <c r="D736" t="b">
         <v>0</v>
       </c>
-      <c r="E736" t="inlineStr"/>
-      <c r="F736" t="inlineStr"/>
-      <c r="G736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -17390,9 +15185,6 @@
       <c r="D737" t="b">
         <v>0</v>
       </c>
-      <c r="E737" t="inlineStr"/>
-      <c r="F737" t="inlineStr"/>
-      <c r="G737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -17413,9 +15205,6 @@
       <c r="D738" t="b">
         <v>1</v>
       </c>
-      <c r="E738" t="inlineStr"/>
-      <c r="F738" t="inlineStr"/>
-      <c r="G738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -17436,9 +15225,6 @@
       <c r="D739" t="b">
         <v>0</v>
       </c>
-      <c r="E739" t="inlineStr"/>
-      <c r="F739" t="inlineStr"/>
-      <c r="G739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -17459,9 +15245,6 @@
       <c r="D740" t="b">
         <v>0</v>
       </c>
-      <c r="E740" t="inlineStr"/>
-      <c r="F740" t="inlineStr"/>
-      <c r="G740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -17482,9 +15265,6 @@
       <c r="D741" t="b">
         <v>0</v>
       </c>
-      <c r="E741" t="inlineStr"/>
-      <c r="F741" t="inlineStr"/>
-      <c r="G741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -17505,9 +15285,6 @@
       <c r="D742" t="b">
         <v>0</v>
       </c>
-      <c r="E742" t="inlineStr"/>
-      <c r="F742" t="inlineStr"/>
-      <c r="G742" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -17528,9 +15305,6 @@
       <c r="D743" t="b">
         <v>0</v>
       </c>
-      <c r="E743" t="inlineStr"/>
-      <c r="F743" t="inlineStr"/>
-      <c r="G743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -17551,9 +15325,6 @@
       <c r="D744" t="b">
         <v>0</v>
       </c>
-      <c r="E744" t="inlineStr"/>
-      <c r="F744" t="inlineStr"/>
-      <c r="G744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -17574,9 +15345,6 @@
       <c r="D745" t="b">
         <v>0</v>
       </c>
-      <c r="E745" t="inlineStr"/>
-      <c r="F745" t="inlineStr"/>
-      <c r="G745" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -17597,9 +15365,6 @@
       <c r="D746" t="b">
         <v>1</v>
       </c>
-      <c r="E746" t="inlineStr"/>
-      <c r="F746" t="inlineStr"/>
-      <c r="G746" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -17620,9 +15385,6 @@
       <c r="D747" t="b">
         <v>1</v>
       </c>
-      <c r="E747" t="inlineStr"/>
-      <c r="F747" t="inlineStr"/>
-      <c r="G747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -17643,9 +15405,6 @@
       <c r="D748" t="b">
         <v>1</v>
       </c>
-      <c r="E748" t="inlineStr"/>
-      <c r="F748" t="inlineStr"/>
-      <c r="G748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -17666,9 +15425,6 @@
       <c r="D749" t="b">
         <v>1</v>
       </c>
-      <c r="E749" t="inlineStr"/>
-      <c r="F749" t="inlineStr"/>
-      <c r="G749" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -17689,9 +15445,6 @@
       <c r="D750" t="b">
         <v>1</v>
       </c>
-      <c r="E750" t="inlineStr"/>
-      <c r="F750" t="inlineStr"/>
-      <c r="G750" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -17712,9 +15465,6 @@
       <c r="D751" t="b">
         <v>1</v>
       </c>
-      <c r="E751" t="inlineStr"/>
-      <c r="F751" t="inlineStr"/>
-      <c r="G751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -17735,9 +15485,6 @@
       <c r="D752" t="b">
         <v>1</v>
       </c>
-      <c r="E752" t="inlineStr"/>
-      <c r="F752" t="inlineStr"/>
-      <c r="G752" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -17758,9 +15505,6 @@
       <c r="D753" t="b">
         <v>1</v>
       </c>
-      <c r="E753" t="inlineStr"/>
-      <c r="F753" t="inlineStr"/>
-      <c r="G753" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -17781,9 +15525,6 @@
       <c r="D754" t="b">
         <v>0</v>
       </c>
-      <c r="E754" t="inlineStr"/>
-      <c r="F754" t="inlineStr"/>
-      <c r="G754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -17804,9 +15545,6 @@
       <c r="D755" t="b">
         <v>0</v>
       </c>
-      <c r="E755" t="inlineStr"/>
-      <c r="F755" t="inlineStr"/>
-      <c r="G755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -17827,9 +15565,6 @@
       <c r="D756" t="b">
         <v>0</v>
       </c>
-      <c r="E756" t="inlineStr"/>
-      <c r="F756" t="inlineStr"/>
-      <c r="G756" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -17850,9 +15585,6 @@
       <c r="D757" t="b">
         <v>0</v>
       </c>
-      <c r="E757" t="inlineStr"/>
-      <c r="F757" t="inlineStr"/>
-      <c r="G757" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -17873,9 +15605,6 @@
       <c r="D758" t="b">
         <v>0</v>
       </c>
-      <c r="E758" t="inlineStr"/>
-      <c r="F758" t="inlineStr"/>
-      <c r="G758" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -17896,9 +15625,6 @@
       <c r="D759" t="b">
         <v>0</v>
       </c>
-      <c r="E759" t="inlineStr"/>
-      <c r="F759" t="inlineStr"/>
-      <c r="G759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -17919,9 +15645,6 @@
       <c r="D760" t="b">
         <v>0</v>
       </c>
-      <c r="E760" t="inlineStr"/>
-      <c r="F760" t="inlineStr"/>
-      <c r="G760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -17942,9 +15665,6 @@
       <c r="D761" t="b">
         <v>1</v>
       </c>
-      <c r="E761" t="inlineStr"/>
-      <c r="F761" t="inlineStr"/>
-      <c r="G761" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -17965,9 +15685,6 @@
       <c r="D762" t="b">
         <v>0</v>
       </c>
-      <c r="E762" t="inlineStr"/>
-      <c r="F762" t="inlineStr"/>
-      <c r="G762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -17988,9 +15705,6 @@
       <c r="D763" t="b">
         <v>0</v>
       </c>
-      <c r="E763" t="inlineStr"/>
-      <c r="F763" t="inlineStr"/>
-      <c r="G763" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -18011,9 +15725,6 @@
       <c r="D764" t="b">
         <v>0</v>
       </c>
-      <c r="E764" t="inlineStr"/>
-      <c r="F764" t="inlineStr"/>
-      <c r="G764" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -18034,9 +15745,6 @@
       <c r="D765" t="b">
         <v>0</v>
       </c>
-      <c r="E765" t="inlineStr"/>
-      <c r="F765" t="inlineStr"/>
-      <c r="G765" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -18057,9 +15765,6 @@
       <c r="D766" t="b">
         <v>0</v>
       </c>
-      <c r="E766" t="inlineStr"/>
-      <c r="F766" t="inlineStr"/>
-      <c r="G766" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -18080,9 +15785,6 @@
       <c r="D767" t="b">
         <v>1</v>
       </c>
-      <c r="E767" t="inlineStr"/>
-      <c r="F767" t="inlineStr"/>
-      <c r="G767" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -18103,9 +15805,6 @@
       <c r="D768" t="b">
         <v>1</v>
       </c>
-      <c r="E768" t="inlineStr"/>
-      <c r="F768" t="inlineStr"/>
-      <c r="G768" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -18126,9 +15825,6 @@
       <c r="D769" t="b">
         <v>1</v>
       </c>
-      <c r="E769" t="inlineStr"/>
-      <c r="F769" t="inlineStr"/>
-      <c r="G769" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -18149,9 +15845,6 @@
       <c r="D770" t="b">
         <v>1</v>
       </c>
-      <c r="E770" t="inlineStr"/>
-      <c r="F770" t="inlineStr"/>
-      <c r="G770" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -18172,9 +15865,6 @@
       <c r="D771" t="b">
         <v>1</v>
       </c>
-      <c r="E771" t="inlineStr"/>
-      <c r="F771" t="inlineStr"/>
-      <c r="G771" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -18195,9 +15885,6 @@
       <c r="D772" t="b">
         <v>0</v>
       </c>
-      <c r="E772" t="inlineStr"/>
-      <c r="F772" t="inlineStr"/>
-      <c r="G772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -18218,9 +15905,6 @@
       <c r="D773" t="b">
         <v>0</v>
       </c>
-      <c r="E773" t="inlineStr"/>
-      <c r="F773" t="inlineStr"/>
-      <c r="G773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -18241,9 +15925,6 @@
       <c r="D774" t="b">
         <v>0</v>
       </c>
-      <c r="E774" t="inlineStr"/>
-      <c r="F774" t="inlineStr"/>
-      <c r="G774" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -18264,9 +15945,6 @@
       <c r="D775" t="b">
         <v>0</v>
       </c>
-      <c r="E775" t="inlineStr"/>
-      <c r="F775" t="inlineStr"/>
-      <c r="G775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -18287,9 +15965,6 @@
       <c r="D776" t="b">
         <v>0</v>
       </c>
-      <c r="E776" t="inlineStr"/>
-      <c r="F776" t="inlineStr"/>
-      <c r="G776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -18310,9 +15985,6 @@
       <c r="D777" t="b">
         <v>0</v>
       </c>
-      <c r="E777" t="inlineStr"/>
-      <c r="F777" t="inlineStr"/>
-      <c r="G777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -18333,9 +16005,6 @@
       <c r="D778" t="b">
         <v>0</v>
       </c>
-      <c r="E778" t="inlineStr"/>
-      <c r="F778" t="inlineStr"/>
-      <c r="G778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -18356,9 +16025,6 @@
       <c r="D779" t="b">
         <v>0</v>
       </c>
-      <c r="E779" t="inlineStr"/>
-      <c r="F779" t="inlineStr"/>
-      <c r="G779" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -18379,9 +16045,6 @@
       <c r="D780" t="b">
         <v>0</v>
       </c>
-      <c r="E780" t="inlineStr"/>
-      <c r="F780" t="inlineStr"/>
-      <c r="G780" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -18402,9 +16065,6 @@
       <c r="D781" t="b">
         <v>0</v>
       </c>
-      <c r="E781" t="inlineStr"/>
-      <c r="F781" t="inlineStr"/>
-      <c r="G781" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -18425,9 +16085,6 @@
       <c r="D782" t="b">
         <v>0</v>
       </c>
-      <c r="E782" t="inlineStr"/>
-      <c r="F782" t="inlineStr"/>
-      <c r="G782" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -18448,9 +16105,6 @@
       <c r="D783" t="b">
         <v>0</v>
       </c>
-      <c r="E783" t="inlineStr"/>
-      <c r="F783" t="inlineStr"/>
-      <c r="G783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -18471,9 +16125,6 @@
       <c r="D784" t="b">
         <v>0</v>
       </c>
-      <c r="E784" t="inlineStr"/>
-      <c r="F784" t="inlineStr"/>
-      <c r="G784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -18494,9 +16145,6 @@
       <c r="D785" t="b">
         <v>0</v>
       </c>
-      <c r="E785" t="inlineStr"/>
-      <c r="F785" t="inlineStr"/>
-      <c r="G785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -18517,9 +16165,6 @@
       <c r="D786" t="b">
         <v>0</v>
       </c>
-      <c r="E786" t="inlineStr"/>
-      <c r="F786" t="inlineStr"/>
-      <c r="G786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -18540,9 +16185,6 @@
       <c r="D787" t="b">
         <v>0</v>
       </c>
-      <c r="E787" t="inlineStr"/>
-      <c r="F787" t="inlineStr"/>
-      <c r="G787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -18563,9 +16205,6 @@
       <c r="D788" t="b">
         <v>1</v>
       </c>
-      <c r="E788" t="inlineStr"/>
-      <c r="F788" t="inlineStr"/>
-      <c r="G788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -18586,9 +16225,6 @@
       <c r="D789" t="b">
         <v>1</v>
       </c>
-      <c r="E789" t="inlineStr"/>
-      <c r="F789" t="inlineStr"/>
-      <c r="G789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -18609,9 +16245,6 @@
       <c r="D790" t="b">
         <v>1</v>
       </c>
-      <c r="E790" t="inlineStr"/>
-      <c r="F790" t="inlineStr"/>
-      <c r="G790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -18632,9 +16265,6 @@
       <c r="D791" t="b">
         <v>1</v>
       </c>
-      <c r="E791" t="inlineStr"/>
-      <c r="F791" t="inlineStr"/>
-      <c r="G791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -18655,9 +16285,6 @@
       <c r="D792" t="b">
         <v>0</v>
       </c>
-      <c r="E792" t="inlineStr"/>
-      <c r="F792" t="inlineStr"/>
-      <c r="G792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -18678,9 +16305,6 @@
       <c r="D793" t="b">
         <v>0</v>
       </c>
-      <c r="E793" t="inlineStr"/>
-      <c r="F793" t="inlineStr"/>
-      <c r="G793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -18701,9 +16325,6 @@
       <c r="D794" t="b">
         <v>0</v>
       </c>
-      <c r="E794" t="inlineStr"/>
-      <c r="F794" t="inlineStr"/>
-      <c r="G794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -18724,9 +16345,6 @@
       <c r="D795" t="b">
         <v>0</v>
       </c>
-      <c r="E795" t="inlineStr"/>
-      <c r="F795" t="inlineStr"/>
-      <c r="G795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -18747,9 +16365,6 @@
       <c r="D796" t="b">
         <v>0</v>
       </c>
-      <c r="E796" t="inlineStr"/>
-      <c r="F796" t="inlineStr"/>
-      <c r="G796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -18770,9 +16385,6 @@
       <c r="D797" t="b">
         <v>0</v>
       </c>
-      <c r="E797" t="inlineStr"/>
-      <c r="F797" t="inlineStr"/>
-      <c r="G797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -18793,9 +16405,6 @@
       <c r="D798" t="b">
         <v>0</v>
       </c>
-      <c r="E798" t="inlineStr"/>
-      <c r="F798" t="inlineStr"/>
-      <c r="G798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -18816,9 +16425,6 @@
       <c r="D799" t="b">
         <v>0</v>
       </c>
-      <c r="E799" t="inlineStr"/>
-      <c r="F799" t="inlineStr"/>
-      <c r="G799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -18839,9 +16445,6 @@
       <c r="D800" t="b">
         <v>0</v>
       </c>
-      <c r="E800" t="inlineStr"/>
-      <c r="F800" t="inlineStr"/>
-      <c r="G800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -18862,9 +16465,6 @@
       <c r="D801" t="b">
         <v>0</v>
       </c>
-      <c r="E801" t="inlineStr"/>
-      <c r="F801" t="inlineStr"/>
-      <c r="G801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -18885,9 +16485,6 @@
       <c r="D802" t="b">
         <v>0</v>
       </c>
-      <c r="E802" t="inlineStr"/>
-      <c r="F802" t="inlineStr"/>
-      <c r="G802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -18908,9 +16505,6 @@
       <c r="D803" t="b">
         <v>0</v>
       </c>
-      <c r="E803" t="inlineStr"/>
-      <c r="F803" t="inlineStr"/>
-      <c r="G803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -18931,9 +16525,6 @@
       <c r="D804" t="b">
         <v>0</v>
       </c>
-      <c r="E804" t="inlineStr"/>
-      <c r="F804" t="inlineStr"/>
-      <c r="G804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -18954,9 +16545,6 @@
       <c r="D805" t="b">
         <v>0</v>
       </c>
-      <c r="E805" t="inlineStr"/>
-      <c r="F805" t="inlineStr"/>
-      <c r="G805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -18977,9 +16565,6 @@
       <c r="D806" t="b">
         <v>0</v>
       </c>
-      <c r="E806" t="inlineStr"/>
-      <c r="F806" t="inlineStr"/>
-      <c r="G806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -19000,9 +16585,6 @@
       <c r="D807" t="b">
         <v>1</v>
       </c>
-      <c r="E807" t="inlineStr"/>
-      <c r="F807" t="inlineStr"/>
-      <c r="G807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -19023,9 +16605,6 @@
       <c r="D808" t="b">
         <v>1</v>
       </c>
-      <c r="E808" t="inlineStr"/>
-      <c r="F808" t="inlineStr"/>
-      <c r="G808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -19046,9 +16625,6 @@
       <c r="D809" t="b">
         <v>1</v>
       </c>
-      <c r="E809" t="inlineStr"/>
-      <c r="F809" t="inlineStr"/>
-      <c r="G809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -19069,9 +16645,6 @@
       <c r="D810" t="b">
         <v>1</v>
       </c>
-      <c r="E810" t="inlineStr"/>
-      <c r="F810" t="inlineStr"/>
-      <c r="G810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -19092,9 +16665,6 @@
       <c r="D811" t="b">
         <v>1</v>
       </c>
-      <c r="E811" t="inlineStr"/>
-      <c r="F811" t="inlineStr"/>
-      <c r="G811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -19115,9 +16685,6 @@
       <c r="D812" t="b">
         <v>1</v>
       </c>
-      <c r="E812" t="inlineStr"/>
-      <c r="F812" t="inlineStr"/>
-      <c r="G812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -19138,9 +16705,6 @@
       <c r="D813" t="b">
         <v>0</v>
       </c>
-      <c r="E813" t="inlineStr"/>
-      <c r="F813" t="inlineStr"/>
-      <c r="G813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -19161,9 +16725,6 @@
       <c r="D814" t="b">
         <v>0</v>
       </c>
-      <c r="E814" t="inlineStr"/>
-      <c r="F814" t="inlineStr"/>
-      <c r="G814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -19184,9 +16745,6 @@
       <c r="D815" t="b">
         <v>0</v>
       </c>
-      <c r="E815" t="inlineStr"/>
-      <c r="F815" t="inlineStr"/>
-      <c r="G815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -19207,9 +16765,6 @@
       <c r="D816" t="b">
         <v>0</v>
       </c>
-      <c r="E816" t="inlineStr"/>
-      <c r="F816" t="inlineStr"/>
-      <c r="G816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -19230,9 +16785,6 @@
       <c r="D817" t="b">
         <v>0</v>
       </c>
-      <c r="E817" t="inlineStr"/>
-      <c r="F817" t="inlineStr"/>
-      <c r="G817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -19253,9 +16805,6 @@
       <c r="D818" t="b">
         <v>0</v>
       </c>
-      <c r="E818" t="inlineStr"/>
-      <c r="F818" t="inlineStr"/>
-      <c r="G818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -19276,9 +16825,6 @@
       <c r="D819" t="b">
         <v>0</v>
       </c>
-      <c r="E819" t="inlineStr"/>
-      <c r="F819" t="inlineStr"/>
-      <c r="G819" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -19299,9 +16845,6 @@
       <c r="D820" t="b">
         <v>0</v>
       </c>
-      <c r="E820" t="inlineStr"/>
-      <c r="F820" t="inlineStr"/>
-      <c r="G820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -19322,9 +16865,6 @@
       <c r="D821" t="b">
         <v>0</v>
       </c>
-      <c r="E821" t="inlineStr"/>
-      <c r="F821" t="inlineStr"/>
-      <c r="G821" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -19345,9 +16885,6 @@
       <c r="D822" t="b">
         <v>0</v>
       </c>
-      <c r="E822" t="inlineStr"/>
-      <c r="F822" t="inlineStr"/>
-      <c r="G822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -19368,9 +16905,6 @@
       <c r="D823" t="b">
         <v>0</v>
       </c>
-      <c r="E823" t="inlineStr"/>
-      <c r="F823" t="inlineStr"/>
-      <c r="G823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -19391,9 +16925,6 @@
       <c r="D824" t="b">
         <v>0</v>
       </c>
-      <c r="E824" t="inlineStr"/>
-      <c r="F824" t="inlineStr"/>
-      <c r="G824" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
